--- a/results/components/gene_names/p5s3.xlsx
+++ b/results/components/gene_names/p5s3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="494">
   <si>
     <t>gene1</t>
   </si>
@@ -22,1429 +22,1480 @@
     <t>gene2</t>
   </si>
   <si>
+    <t>fd59A</t>
+  </si>
+  <si>
+    <t>tra2</t>
+  </si>
+  <si>
+    <t>hdc</t>
+  </si>
+  <si>
+    <t>Idgf4</t>
+  </si>
+  <si>
+    <t>Mkp3</t>
+  </si>
+  <si>
+    <t>Eip74EF</t>
+  </si>
+  <si>
+    <t>cbt</t>
+  </si>
+  <si>
+    <t>Hr78</t>
+  </si>
+  <si>
+    <t>sar1</t>
+  </si>
+  <si>
+    <t>ea</t>
+  </si>
+  <si>
+    <t>Ef1gamma</t>
+  </si>
+  <si>
+    <t>tin</t>
+  </si>
+  <si>
+    <t>sli</t>
+  </si>
+  <si>
+    <t>sax</t>
+  </si>
+  <si>
+    <t>up</t>
+  </si>
+  <si>
+    <t>asf1</t>
+  </si>
+  <si>
+    <t>Galpha73B</t>
+  </si>
+  <si>
+    <t>cathD</t>
+  </si>
+  <si>
+    <t>phyl</t>
+  </si>
+  <si>
+    <t>bnl</t>
+  </si>
+  <si>
+    <t>cin</t>
+  </si>
+  <si>
+    <t>Tak1</t>
+  </si>
+  <si>
+    <t>Tm1</t>
+  </si>
+  <si>
+    <t>inaC</t>
+  </si>
+  <si>
+    <t>sll</t>
+  </si>
+  <si>
+    <t>Sry-delta</t>
+  </si>
+  <si>
+    <t>capu</t>
+  </si>
+  <si>
+    <t>Msp-300</t>
+  </si>
+  <si>
+    <t>Ddx1</t>
+  </si>
+  <si>
+    <t>gkt</t>
+  </si>
+  <si>
+    <t>svr</t>
+  </si>
+  <si>
+    <t>Jafrac2</t>
+  </si>
+  <si>
+    <t>Dok</t>
+  </si>
+  <si>
+    <t>Cyt-c-d</t>
+  </si>
+  <si>
+    <t>Set2</t>
+  </si>
+  <si>
+    <t>Akap200</t>
+  </si>
+  <si>
+    <t>14-3-3zeta</t>
+  </si>
+  <si>
+    <t>hyd</t>
+  </si>
+  <si>
+    <t>CG9520</t>
+  </si>
+  <si>
+    <t>Antp</t>
+  </si>
+  <si>
+    <t>MED11</t>
+  </si>
+  <si>
+    <t>Cks30A</t>
+  </si>
+  <si>
+    <t>Rack1</t>
+  </si>
+  <si>
+    <t>Hem</t>
+  </si>
+  <si>
+    <t>sty</t>
+  </si>
+  <si>
+    <t>Dhc64C</t>
+  </si>
+  <si>
+    <t>Apc2</t>
+  </si>
+  <si>
+    <t>Fmr1</t>
+  </si>
+  <si>
+    <t>glec</t>
+  </si>
+  <si>
+    <t>zfh1</t>
+  </si>
+  <si>
+    <t>mam</t>
+  </si>
+  <si>
+    <t>dsf</t>
+  </si>
+  <si>
+    <t>par-6</t>
+  </si>
+  <si>
+    <t>Appl</t>
+  </si>
+  <si>
+    <t>foxo</t>
+  </si>
+  <si>
+    <t>lilli</t>
+  </si>
+  <si>
+    <t>RpL30</t>
+  </si>
+  <si>
+    <t>Cp1</t>
+  </si>
+  <si>
+    <t>Ca-alpha1D</t>
+  </si>
+  <si>
+    <t>chico</t>
+  </si>
+  <si>
+    <t>Arp66B</t>
+  </si>
+  <si>
+    <t>Src64B</t>
+  </si>
+  <si>
+    <t>bt</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>dup</t>
+  </si>
+  <si>
+    <t>Moe</t>
+  </si>
+  <si>
+    <t>Pvr</t>
+  </si>
+  <si>
+    <t>l(2)efl</t>
+  </si>
+  <si>
+    <t>tld</t>
+  </si>
+  <si>
+    <t>trio</t>
+  </si>
+  <si>
+    <t>l(2)37Cc</t>
+  </si>
+  <si>
+    <t>spen</t>
+  </si>
+  <si>
+    <t>eve</t>
+  </si>
+  <si>
+    <t>Pk92B</t>
+  </si>
+  <si>
+    <t>dpp</t>
+  </si>
+  <si>
+    <t>Su(var)2-10</t>
+  </si>
+  <si>
+    <t>l(3)mbt</t>
+  </si>
+  <si>
+    <t>dei</t>
+  </si>
+  <si>
+    <t>eg</t>
+  </si>
+  <si>
+    <t>Nrx-IV</t>
+  </si>
+  <si>
+    <t>tkv</t>
+  </si>
+  <si>
+    <t>oaf</t>
+  </si>
+  <si>
+    <t>esg</t>
+  </si>
+  <si>
+    <t>apt</t>
+  </si>
+  <si>
+    <t>cas</t>
+  </si>
+  <si>
+    <t>Nrt</t>
+  </si>
+  <si>
+    <t>dock</t>
+  </si>
+  <si>
+    <t>yrt</t>
+  </si>
+  <si>
+    <t>kis</t>
+  </si>
+  <si>
+    <t>osa</t>
+  </si>
+  <si>
+    <t>pbl</t>
+  </si>
+  <si>
+    <t>Hmgs</t>
+  </si>
+  <si>
+    <t>sas</t>
+  </si>
+  <si>
+    <t>Rab7</t>
+  </si>
+  <si>
+    <t>mri</t>
+  </si>
+  <si>
+    <t>ash2</t>
+  </si>
+  <si>
+    <t>pav</t>
+  </si>
+  <si>
+    <t>qm</t>
+  </si>
+  <si>
+    <t>Mhc</t>
+  </si>
+  <si>
+    <t>Alk</t>
+  </si>
+  <si>
+    <t>fs(2)ltoPP43</t>
+  </si>
+  <si>
+    <t>mfas</t>
+  </si>
+  <si>
+    <t>ksr</t>
+  </si>
+  <si>
+    <t>Tl</t>
+  </si>
+  <si>
+    <t>CG9104</t>
+  </si>
+  <si>
+    <t>jing</t>
+  </si>
+  <si>
+    <t>Oseg1</t>
+  </si>
+  <si>
+    <t>Krn</t>
+  </si>
+  <si>
+    <t>sbb</t>
+  </si>
+  <si>
+    <t>Abl</t>
+  </si>
+  <si>
+    <t>rdx</t>
+  </si>
+  <si>
+    <t>Pka-C3</t>
+  </si>
+  <si>
+    <t>p53</t>
+  </si>
+  <si>
+    <t>Aph-4</t>
+  </si>
+  <si>
+    <t>Cka</t>
+  </si>
+  <si>
+    <t>bs</t>
+  </si>
+  <si>
+    <t>Khc</t>
+  </si>
+  <si>
+    <t>alph</t>
+  </si>
+  <si>
+    <t>CG9445</t>
+  </si>
+  <si>
+    <t>kuk</t>
+  </si>
+  <si>
+    <t>CtBP</t>
+  </si>
+  <si>
+    <t>cos</t>
+  </si>
+  <si>
+    <t>rad50</t>
+  </si>
+  <si>
+    <t>ppan</t>
+  </si>
+  <si>
+    <t>mus304</t>
+  </si>
+  <si>
+    <t>ex</t>
+  </si>
+  <si>
+    <t>bowl</t>
+  </si>
+  <si>
+    <t>Sxl</t>
+  </si>
+  <si>
+    <t>Wnt5</t>
+  </si>
+  <si>
+    <t>raw</t>
+  </si>
+  <si>
+    <t>ey</t>
+  </si>
+  <si>
+    <t>bap</t>
+  </si>
+  <si>
+    <t>pdm2</t>
+  </si>
+  <si>
+    <t>lola</t>
+  </si>
+  <si>
+    <t>Mef2</t>
+  </si>
+  <si>
+    <t>bcd</t>
+  </si>
+  <si>
+    <t>bun</t>
+  </si>
+  <si>
+    <t>beta4GalNAcTA</t>
+  </si>
+  <si>
+    <t>how</t>
+  </si>
+  <si>
+    <t>dib</t>
+  </si>
+  <si>
+    <t>Apc</t>
+  </si>
+  <si>
+    <t>Vhl</t>
+  </si>
+  <si>
+    <t>Rab5</t>
+  </si>
+  <si>
+    <t>Ice</t>
+  </si>
+  <si>
+    <t>dco</t>
+  </si>
+  <si>
+    <t>LIMK1</t>
+  </si>
+  <si>
+    <t>Pcaf</t>
+  </si>
+  <si>
+    <t>betaTub56D</t>
+  </si>
+  <si>
+    <t>Mlc1</t>
+  </si>
+  <si>
+    <t>CG1942</t>
+  </si>
+  <si>
+    <t>Fas3</t>
+  </si>
+  <si>
+    <t>gl</t>
+  </si>
+  <si>
+    <t>Cip4</t>
+  </si>
+  <si>
+    <t>rux</t>
+  </si>
+  <si>
+    <t>cbx</t>
+  </si>
+  <si>
+    <t>enok</t>
+  </si>
+  <si>
+    <t>CG6416</t>
+  </si>
+  <si>
+    <t>aft</t>
+  </si>
+  <si>
+    <t>sec23</t>
+  </si>
+  <si>
+    <t>Bap60</t>
+  </si>
+  <si>
+    <t>hkl</t>
+  </si>
+  <si>
+    <t>RhoGAP68F</t>
+  </si>
+  <si>
+    <t>msi</t>
+  </si>
+  <si>
+    <t>fog</t>
+  </si>
+  <si>
+    <t>G-ialpha65A</t>
+  </si>
+  <si>
+    <t>NetB</t>
+  </si>
+  <si>
+    <t>Hs2st</t>
+  </si>
+  <si>
+    <t>Mtl</t>
+  </si>
+  <si>
+    <t>cort</t>
+  </si>
+  <si>
+    <t>lin</t>
+  </si>
+  <si>
+    <t>E2f</t>
+  </si>
+  <si>
+    <t>Scgdelta</t>
+  </si>
+  <si>
+    <t>Arc42</t>
+  </si>
+  <si>
+    <t>cher</t>
+  </si>
+  <si>
+    <t>chinmo</t>
+  </si>
+  <si>
+    <t>sls</t>
+  </si>
+  <si>
+    <t>CG32082</t>
+  </si>
+  <si>
+    <t>ics</t>
+  </si>
+  <si>
+    <t>sktl</t>
+  </si>
+  <si>
+    <t>Axn</t>
+  </si>
+  <si>
+    <t>meso18E</t>
+  </si>
+  <si>
+    <t>dl</t>
+  </si>
+  <si>
+    <t>E(z)</t>
+  </si>
+  <si>
+    <t>Yp1</t>
+  </si>
+  <si>
+    <t>ftz-f1</t>
+  </si>
+  <si>
+    <t>Chc</t>
+  </si>
+  <si>
+    <t>Traf6</t>
+  </si>
+  <si>
+    <t>Akt1</t>
+  </si>
+  <si>
+    <t>boss</t>
+  </si>
+  <si>
+    <t>zfh2</t>
+  </si>
+  <si>
+    <t>Myo61F</t>
+  </si>
+  <si>
+    <t>jar</t>
+  </si>
+  <si>
+    <t>lic</t>
+  </si>
+  <si>
+    <t>l(1)G0289</t>
+  </si>
+  <si>
+    <t>glu</t>
+  </si>
+  <si>
+    <t>Ptpmeg</t>
+  </si>
+  <si>
+    <t>Idgf5</t>
+  </si>
+  <si>
+    <t>Myo31DF</t>
+  </si>
+  <si>
+    <t>Iswi</t>
+  </si>
+  <si>
+    <t>sqd</t>
+  </si>
+  <si>
+    <t>CG17739</t>
+  </si>
+  <si>
+    <t>Sh</t>
+  </si>
+  <si>
+    <t>Caf1</t>
+  </si>
+  <si>
+    <t>hpo</t>
+  </si>
+  <si>
+    <t>tup</t>
+  </si>
+  <si>
+    <t>ImpE3</t>
+  </si>
+  <si>
+    <t>CG13850</t>
+  </si>
+  <si>
+    <t>drk</t>
+  </si>
+  <si>
+    <t>Dcp-1</t>
+  </si>
+  <si>
+    <t>xl6</t>
+  </si>
+  <si>
+    <t>sina</t>
+  </si>
+  <si>
+    <t>RhoGAPp190</t>
+  </si>
+  <si>
+    <t>emb</t>
+  </si>
+  <si>
+    <t>CG10641</t>
+  </si>
+  <si>
+    <t>Dap160</t>
+  </si>
+  <si>
+    <t>crc</t>
+  </si>
+  <si>
+    <t>eIF-4E</t>
+  </si>
+  <si>
+    <t>knrl</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>tow</t>
+  </si>
+  <si>
+    <t>uzip</t>
+  </si>
+  <si>
+    <t>Crk</t>
+  </si>
+  <si>
+    <t>tamo</t>
+  </si>
+  <si>
+    <t>E2f2</t>
+  </si>
+  <si>
+    <t>Dscam</t>
+  </si>
+  <si>
+    <t>lva</t>
+  </si>
+  <si>
+    <t>emc</t>
+  </si>
+  <si>
+    <t>poe</t>
+  </si>
+  <si>
+    <t>Eip71CD</t>
+  </si>
+  <si>
+    <t>sav</t>
+  </si>
+  <si>
+    <t>Eip63F-1</t>
+  </si>
+  <si>
+    <t>mbt</t>
+  </si>
+  <si>
+    <t>qkr58E-3</t>
+  </si>
+  <si>
+    <t>stumps</t>
+  </si>
+  <si>
+    <t>CG8216</t>
+  </si>
+  <si>
+    <t>ssh</t>
+  </si>
+  <si>
+    <t>SelG</t>
+  </si>
+  <si>
+    <t>scra</t>
+  </si>
+  <si>
+    <t>sdt</t>
+  </si>
+  <si>
+    <t>trc</t>
+  </si>
+  <si>
+    <t>ap</t>
+  </si>
+  <si>
+    <t>elav</t>
+  </si>
+  <si>
+    <t>CycA</t>
+  </si>
+  <si>
+    <t>bon</t>
+  </si>
+  <si>
+    <t>spn-A</t>
+  </si>
+  <si>
+    <t>CG8247</t>
+  </si>
+  <si>
+    <t>Pk61C</t>
+  </si>
+  <si>
+    <t>vlc</t>
+  </si>
+  <si>
+    <t>crol</t>
+  </si>
+  <si>
+    <t>Lim1</t>
+  </si>
+  <si>
+    <t>Sulf1</t>
+  </si>
+  <si>
+    <t>tok</t>
+  </si>
+  <si>
+    <t>ird5</t>
+  </si>
+  <si>
+    <t>Syx1A</t>
+  </si>
+  <si>
     <t>dsx</t>
   </si>
   <si>
-    <t>CG9104</t>
+    <t>rdo</t>
+  </si>
+  <si>
+    <t>Spred</t>
+  </si>
+  <si>
+    <t>Abd-B</t>
+  </si>
+  <si>
+    <t>CycB</t>
+  </si>
+  <si>
+    <t>toe</t>
+  </si>
+  <si>
+    <t>Optix</t>
+  </si>
+  <si>
+    <t>ecd</t>
+  </si>
+  <si>
+    <t>mmy</t>
+  </si>
+  <si>
+    <t>neur</t>
+  </si>
+  <si>
+    <t>CycE</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>Lac</t>
+  </si>
+  <si>
+    <t>Hr46</t>
+  </si>
+  <si>
+    <t>scrib</t>
+  </si>
+  <si>
+    <t>emp</t>
+  </si>
+  <si>
+    <t>klar</t>
+  </si>
+  <si>
+    <t>chif</t>
+  </si>
+  <si>
+    <t>gro</t>
+  </si>
+  <si>
+    <t>CG34450</t>
+  </si>
+  <si>
+    <t>MYPT-75D</t>
+  </si>
+  <si>
+    <t>CG9769</t>
+  </si>
+  <si>
+    <t>run</t>
+  </si>
+  <si>
+    <t>Pi3K92E</t>
+  </si>
+  <si>
+    <t>Trl</t>
+  </si>
+  <si>
+    <t>puc</t>
+  </si>
+  <si>
+    <t>ALiX</t>
+  </si>
+  <si>
+    <t>eff</t>
+  </si>
+  <si>
+    <t>tou</t>
+  </si>
+  <si>
+    <t>Mmp2</t>
+  </si>
+  <si>
+    <t>mask</t>
+  </si>
+  <si>
+    <t>mth</t>
+  </si>
+  <si>
+    <t>ct</t>
+  </si>
+  <si>
+    <t>drm</t>
+  </si>
+  <si>
+    <t>dpn</t>
+  </si>
+  <si>
+    <t>dj</t>
+  </si>
+  <si>
+    <t>wee</t>
+  </si>
+  <si>
+    <t>dom</t>
+  </si>
+  <si>
+    <t>ash1</t>
+  </si>
+  <si>
+    <t>Ank2</t>
+  </si>
+  <si>
+    <t>flfl</t>
+  </si>
+  <si>
+    <t>Jra</t>
+  </si>
+  <si>
+    <t>eya</t>
+  </si>
+  <si>
+    <t>numb</t>
+  </si>
+  <si>
+    <t>fred</t>
+  </si>
+  <si>
+    <t>spir</t>
+  </si>
+  <si>
+    <t>tra</t>
+  </si>
+  <si>
+    <t>Rpd3</t>
+  </si>
+  <si>
+    <t>kuz</t>
+  </si>
+  <si>
+    <t>fl(2)d</t>
+  </si>
+  <si>
+    <t>form3</t>
+  </si>
+  <si>
+    <t>pcm</t>
+  </si>
+  <si>
+    <t>flw</t>
+  </si>
+  <si>
+    <t>Src42A</t>
+  </si>
+  <si>
+    <t>Cct1</t>
+  </si>
+  <si>
+    <t>E(bx)</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>bib</t>
+  </si>
+  <si>
+    <t>loco</t>
+  </si>
+  <si>
+    <t>Mitf</t>
+  </si>
+  <si>
+    <t>yellow-f</t>
+  </si>
+  <si>
+    <t>Dlic2</t>
+  </si>
+  <si>
+    <t>fs(1)K10</t>
+  </si>
+  <si>
+    <t>CG12301</t>
+  </si>
+  <si>
+    <t>tutl</t>
+  </si>
+  <si>
+    <t>stg</t>
+  </si>
+  <si>
+    <t>rhea</t>
+  </si>
+  <si>
+    <t>dos</t>
+  </si>
+  <si>
+    <t>CG18369</t>
+  </si>
+  <si>
+    <t>pot</t>
+  </si>
+  <si>
+    <t>MED4</t>
+  </si>
+  <si>
+    <t>Dif</t>
+  </si>
+  <si>
+    <t>Rca1</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>Sema-2a</t>
+  </si>
+  <si>
+    <t>ine</t>
+  </si>
+  <si>
+    <t>G-salpha60A</t>
+  </si>
+  <si>
+    <t>Rho1</t>
+  </si>
+  <si>
+    <t>l(2)gd1</t>
+  </si>
+  <si>
+    <t>Prm</t>
+  </si>
+  <si>
+    <t>msk</t>
+  </si>
+  <si>
+    <t>18w</t>
+  </si>
+  <si>
+    <t>ry</t>
+  </si>
+  <si>
+    <t>Atg5</t>
+  </si>
+  <si>
+    <t>Pak</t>
+  </si>
+  <si>
+    <t>l(2)gl</t>
+  </si>
+  <si>
+    <t>Psn</t>
+  </si>
+  <si>
+    <t>lmd</t>
+  </si>
+  <si>
+    <t>hyx</t>
+  </si>
+  <si>
+    <t>Syb</t>
+  </si>
+  <si>
+    <t>LCBP1</t>
+  </si>
+  <si>
+    <t>CG2678</t>
+  </si>
+  <si>
+    <t>kay</t>
+  </si>
+  <si>
+    <t>bigmax</t>
+  </si>
+  <si>
+    <t>Gtp-bp</t>
+  </si>
+  <si>
+    <t>twi</t>
+  </si>
+  <si>
+    <t>Lis-1</t>
+  </si>
+  <si>
+    <t>kkv</t>
+  </si>
+  <si>
+    <t>btl</t>
+  </si>
+  <si>
+    <t>CG4945</t>
+  </si>
+  <si>
+    <t>CG3987</t>
+  </si>
+  <si>
+    <t>wus</t>
+  </si>
+  <si>
+    <t>shot</t>
+  </si>
+  <si>
+    <t>slam</t>
+  </si>
+  <si>
+    <t>Dad</t>
+  </si>
+  <si>
+    <t>nej</t>
+  </si>
+  <si>
+    <t>chrw</t>
+  </si>
+  <si>
+    <t>fal</t>
+  </si>
+  <si>
+    <t>bnb</t>
+  </si>
+  <si>
+    <t>acj6</t>
+  </si>
+  <si>
+    <t>RhoL</t>
+  </si>
+  <si>
+    <t>tud</t>
+  </si>
+  <si>
+    <t>dome</t>
+  </si>
+  <si>
+    <t>CkIIalpha</t>
+  </si>
+  <si>
+    <t>gbb</t>
+  </si>
+  <si>
+    <t>Idgf2</t>
+  </si>
+  <si>
+    <t>CG17221</t>
+  </si>
+  <si>
+    <t>Btk29A</t>
   </si>
   <si>
     <t>CG12896</t>
   </si>
   <si>
+    <t>wal</t>
+  </si>
+  <si>
+    <t>Lcp65Ag1</t>
+  </si>
+  <si>
+    <t>exu</t>
+  </si>
+  <si>
+    <t>MED24</t>
+  </si>
+  <si>
+    <t>drl</t>
+  </si>
+  <si>
+    <t>Pde8</t>
+  </si>
+  <si>
+    <t>FKBP59</t>
+  </si>
+  <si>
+    <t>tral</t>
+  </si>
+  <si>
+    <t>shg</t>
+  </si>
+  <si>
+    <t>sn</t>
+  </si>
+  <si>
+    <t>rg</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>twf</t>
+  </si>
+  <si>
+    <t>noc</t>
+  </si>
+  <si>
+    <t>Atg6</t>
+  </si>
+  <si>
+    <t>Taf4</t>
+  </si>
+  <si>
+    <t>mbl</t>
+  </si>
+  <si>
+    <t>stil</t>
+  </si>
+  <si>
+    <t>sgl</t>
+  </si>
+  <si>
+    <t>dpld</t>
+  </si>
+  <si>
+    <t>Sur</t>
+  </si>
+  <si>
+    <t>Dat</t>
+  </si>
+  <si>
+    <t>PhKgamma</t>
+  </si>
+  <si>
+    <t>Mbs</t>
+  </si>
+  <si>
+    <t>PebIII</t>
+  </si>
+  <si>
     <t>ben</t>
   </si>
   <si>
-    <t>Idgf4</t>
-  </si>
-  <si>
-    <t>tow</t>
-  </si>
-  <si>
-    <t>chn</t>
-  </si>
-  <si>
-    <t>jing</t>
-  </si>
-  <si>
-    <t>Tl</t>
-  </si>
-  <si>
-    <t>Psn</t>
-  </si>
-  <si>
-    <t>Ark</t>
-  </si>
-  <si>
-    <t>Lis-1</t>
-  </si>
-  <si>
-    <t>shn</t>
+    <t>ast</t>
+  </si>
+  <si>
+    <t>dec-1</t>
+  </si>
+  <si>
+    <t>Mmp1</t>
+  </si>
+  <si>
+    <t>Atpalpha</t>
+  </si>
+  <si>
+    <t>Patj</t>
+  </si>
+  <si>
+    <t>G-oalpha47A</t>
+  </si>
+  <si>
+    <t>da</t>
+  </si>
+  <si>
+    <t>shrb</t>
+  </si>
+  <si>
+    <t>CG16719</t>
+  </si>
+  <si>
+    <t>ix</t>
+  </si>
+  <si>
+    <t>grp</t>
+  </si>
+  <si>
+    <t>dally</t>
+  </si>
+  <si>
+    <t>tub</t>
+  </si>
+  <si>
+    <t>CG2681</t>
+  </si>
+  <si>
+    <t>Sobp</t>
+  </si>
+  <si>
+    <t>cta</t>
+  </si>
+  <si>
+    <t>pnut</t>
+  </si>
+  <si>
+    <t>CG32486</t>
+  </si>
+  <si>
+    <t>CG6372</t>
+  </si>
+  <si>
+    <t>CG9509</t>
+  </si>
+  <si>
+    <t>Sema-1b</t>
+  </si>
+  <si>
+    <t>cnk</t>
+  </si>
+  <si>
+    <t>Pink1</t>
+  </si>
+  <si>
+    <t>pyd</t>
+  </si>
+  <si>
+    <t>ytr</t>
+  </si>
+  <si>
+    <t>pio</t>
+  </si>
+  <si>
+    <t>nmo</t>
+  </si>
+  <si>
+    <t>pn</t>
+  </si>
+  <si>
+    <t>alien</t>
+  </si>
+  <si>
+    <t>Glycogenin</t>
+  </si>
+  <si>
+    <t>sgg</t>
+  </si>
+  <si>
+    <t>Eip63E</t>
+  </si>
+  <si>
+    <t>wrapper</t>
+  </si>
+  <si>
+    <t>tsh</t>
+  </si>
+  <si>
+    <t>tum</t>
+  </si>
+  <si>
+    <t>Tina-1</t>
+  </si>
+  <si>
+    <t>Idgf1</t>
+  </si>
+  <si>
+    <t>blow</t>
+  </si>
+  <si>
+    <t>dnc</t>
+  </si>
+  <si>
+    <t>alpha-Spec</t>
+  </si>
+  <si>
+    <t>bhr</t>
+  </si>
+  <si>
+    <t>wupA</t>
+  </si>
+  <si>
+    <t>by</t>
+  </si>
+  <si>
+    <t>baz</t>
+  </si>
+  <si>
+    <t>sns</t>
+  </si>
+  <si>
+    <t>mib1</t>
+  </si>
+  <si>
+    <t>cnc</t>
+  </si>
+  <si>
+    <t>esc</t>
+  </si>
+  <si>
+    <t>SelD</t>
   </si>
   <si>
     <t>dah</t>
   </si>
   <si>
-    <t>sqd</t>
-  </si>
-  <si>
-    <t>Patj</t>
-  </si>
-  <si>
-    <t>fred</t>
-  </si>
-  <si>
-    <t>ine</t>
-  </si>
-  <si>
-    <t>dmt</t>
+    <t>fw</t>
+  </si>
+  <si>
+    <t>CadN</t>
+  </si>
+  <si>
+    <t>Borr</t>
+  </si>
+  <si>
+    <t>abd-A</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>chic</t>
+  </si>
+  <si>
+    <t>Sb</t>
+  </si>
+  <si>
+    <t>siz</t>
+  </si>
+  <si>
+    <t>disco</t>
+  </si>
+  <si>
+    <t>frc</t>
+  </si>
+  <si>
+    <t>th</t>
+  </si>
+  <si>
+    <t>pnr</t>
+  </si>
+  <si>
+    <t>ofs</t>
+  </si>
+  <si>
+    <t>Dl</t>
+  </si>
+  <si>
+    <t>Abi</t>
+  </si>
+  <si>
+    <t>Pgant35A</t>
+  </si>
+  <si>
+    <t>Hs6st</t>
+  </si>
+  <si>
+    <t>Ephrin</t>
   </si>
   <si>
     <t>spin</t>
   </si>
   <si>
-    <t>dj</t>
-  </si>
-  <si>
-    <t>Nf1</t>
-  </si>
-  <si>
-    <t>slam</t>
-  </si>
-  <si>
-    <t>rdx</t>
-  </si>
-  <si>
-    <t>LCBP1</t>
-  </si>
-  <si>
-    <t>Dhc64C</t>
-  </si>
-  <si>
-    <t>Galpha73B</t>
-  </si>
-  <si>
-    <t>flw</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>raw</t>
-  </si>
-  <si>
-    <t>CG1942</t>
-  </si>
-  <si>
-    <t>CdsA</t>
-  </si>
-  <si>
-    <t>Cip4</t>
-  </si>
-  <si>
-    <t>tin</t>
-  </si>
-  <si>
-    <t>CG32082</t>
-  </si>
-  <si>
-    <t>eff</t>
-  </si>
-  <si>
-    <t>osa</t>
-  </si>
-  <si>
-    <t>p53</t>
-  </si>
-  <si>
-    <t>zfh2</t>
-  </si>
-  <si>
-    <t>cic</t>
-  </si>
-  <si>
-    <t>scyl</t>
-  </si>
-  <si>
-    <t>sle</t>
-  </si>
-  <si>
-    <t>tral</t>
-  </si>
-  <si>
-    <t>Aph-4</t>
-  </si>
-  <si>
-    <t>poe</t>
-  </si>
-  <si>
-    <t>Su(var)2-10</t>
-  </si>
-  <si>
-    <t>mbl</t>
-  </si>
-  <si>
-    <t>Lcp65Ag1</t>
-  </si>
-  <si>
-    <t>Myo31DF</t>
-  </si>
-  <si>
-    <t>CG16719</t>
+    <t>Alh</t>
+  </si>
+  <si>
+    <t>Dredd</t>
+  </si>
+  <si>
+    <t>B4</t>
+  </si>
+  <si>
+    <t>xmas-2</t>
+  </si>
+  <si>
+    <t>cactin</t>
+  </si>
+  <si>
+    <t>hep</t>
+  </si>
+  <si>
+    <t>ken</t>
   </si>
   <si>
     <t>Es2</t>
   </si>
   <si>
-    <t>alien</t>
-  </si>
-  <si>
-    <t>Eip63F-1</t>
-  </si>
-  <si>
-    <t>tra</t>
-  </si>
-  <si>
-    <t>dpn</t>
-  </si>
-  <si>
-    <t>pnr</t>
-  </si>
-  <si>
-    <t>Rack1</t>
+    <t>prod</t>
+  </si>
+  <si>
+    <t>brat</t>
+  </si>
+  <si>
+    <t>fs(1)M3</t>
+  </si>
+  <si>
+    <t>CG34417</t>
+  </si>
+  <si>
+    <t>sec13</t>
+  </si>
+  <si>
+    <t>Not1</t>
+  </si>
+  <si>
+    <t>prd</t>
+  </si>
+  <si>
+    <t>Su(H)</t>
+  </si>
+  <si>
+    <t>Pop2</t>
+  </si>
+  <si>
+    <t>Cyp1</t>
+  </si>
+  <si>
+    <t>caup</t>
+  </si>
+  <si>
+    <t>Su(z)12</t>
+  </si>
+  <si>
+    <t>Pkn</t>
   </si>
   <si>
     <t>pros</t>
   </si>
   <si>
-    <t>pnt</t>
-  </si>
-  <si>
-    <t>wupA</t>
-  </si>
-  <si>
-    <t>Pvr</t>
-  </si>
-  <si>
-    <t>eIF-4a</t>
-  </si>
-  <si>
-    <t>ey</t>
-  </si>
-  <si>
-    <t>t</t>
-  </si>
-  <si>
-    <t>CG8149</t>
-  </si>
-  <si>
-    <t>emb</t>
-  </si>
-  <si>
-    <t>Dok</t>
-  </si>
-  <si>
-    <t>CG4945</t>
-  </si>
-  <si>
-    <t>tkv</t>
-  </si>
-  <si>
-    <t>vlc</t>
-  </si>
-  <si>
-    <t>bon</t>
-  </si>
-  <si>
-    <t>bnl</t>
-  </si>
-  <si>
-    <t>Ice</t>
-  </si>
-  <si>
-    <t>rdo</t>
-  </si>
-  <si>
-    <t>cort</t>
-  </si>
-  <si>
-    <t>frc</t>
-  </si>
-  <si>
-    <t>CG8216</t>
-  </si>
-  <si>
-    <t>ea</t>
-  </si>
-  <si>
-    <t>cnc</t>
-  </si>
-  <si>
-    <t>bib</t>
-  </si>
-  <si>
-    <t>rux</t>
-  </si>
-  <si>
-    <t>aft</t>
-  </si>
-  <si>
-    <t>cher</t>
-  </si>
-  <si>
-    <t>sktl</t>
-  </si>
-  <si>
-    <t>jumu</t>
-  </si>
-  <si>
-    <t>numb</t>
-  </si>
-  <si>
-    <t>sina</t>
-  </si>
-  <si>
-    <t>l(3)mbt</t>
-  </si>
-  <si>
-    <t>pn</t>
-  </si>
-  <si>
-    <t>bowl</t>
-  </si>
-  <si>
-    <t>sdt</t>
-  </si>
-  <si>
-    <t>Abd-B</t>
-  </si>
-  <si>
-    <t>fs(2)ltoPP43</t>
-  </si>
-  <si>
-    <t>Pop2</t>
-  </si>
-  <si>
-    <t>Hem</t>
-  </si>
-  <si>
-    <t>mri</t>
-  </si>
-  <si>
-    <t>CG9520</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Cka</t>
-  </si>
-  <si>
-    <t>Eip74EF</t>
-  </si>
-  <si>
-    <t>wal</t>
-  </si>
-  <si>
-    <t>kuk</t>
-  </si>
-  <si>
-    <t>Nrx-IV</t>
-  </si>
-  <si>
-    <t>fru</t>
-  </si>
-  <si>
-    <t>asf1</t>
-  </si>
-  <si>
-    <t>Rca1</t>
-  </si>
-  <si>
-    <t>fs(1)K10</t>
-  </si>
-  <si>
-    <t>wrapper</t>
-  </si>
-  <si>
-    <t>Tina-1</t>
-  </si>
-  <si>
-    <t>vap</t>
-  </si>
-  <si>
-    <t>Idgf5</t>
-  </si>
-  <si>
-    <t>lmd</t>
-  </si>
-  <si>
-    <t>lic</t>
-  </si>
-  <si>
-    <t>bun</t>
-  </si>
-  <si>
-    <t>Scgdelta</t>
-  </si>
-  <si>
-    <t>Ald</t>
-  </si>
-  <si>
-    <t>18w</t>
-  </si>
-  <si>
-    <t>Dscam</t>
-  </si>
-  <si>
-    <t>hdc</t>
-  </si>
-  <si>
-    <t>SelD</t>
-  </si>
-  <si>
-    <t>Rbp9</t>
-  </si>
-  <si>
-    <t>wus</t>
-  </si>
-  <si>
-    <t>Ddx1</t>
-  </si>
-  <si>
-    <t>par-6</t>
-  </si>
-  <si>
-    <t>FKBP59</t>
-  </si>
-  <si>
-    <t>opa</t>
-  </si>
-  <si>
-    <t>Idgf1</t>
-  </si>
-  <si>
-    <t>gro</t>
-  </si>
-  <si>
-    <t>lva</t>
-  </si>
-  <si>
-    <t>Cp1</t>
-  </si>
-  <si>
-    <t>ofs</t>
-  </si>
-  <si>
-    <t>sec13</t>
-  </si>
-  <si>
-    <t>sn</t>
-  </si>
-  <si>
-    <t>neur</t>
-  </si>
-  <si>
-    <t>car</t>
-  </si>
-  <si>
-    <t>G-salpha60A</t>
-  </si>
-  <si>
-    <t>drk</t>
-  </si>
-  <si>
-    <t>Nrt</t>
-  </si>
-  <si>
-    <t>CG14995</t>
-  </si>
-  <si>
-    <t>CycE</t>
-  </si>
-  <si>
-    <t>mfas</t>
-  </si>
-  <si>
-    <t>tra2</t>
-  </si>
-  <si>
-    <t>puc</t>
-  </si>
-  <si>
-    <t>ct</t>
-  </si>
-  <si>
-    <t>xmas-2</t>
-  </si>
-  <si>
-    <t>capu</t>
-  </si>
-  <si>
-    <t>twi</t>
-  </si>
-  <si>
-    <t>spen</t>
-  </si>
-  <si>
-    <t>dco</t>
-  </si>
-  <si>
-    <t>bt</t>
-  </si>
-  <si>
-    <t>Sb</t>
-  </si>
-  <si>
-    <t>Eip63E</t>
-  </si>
-  <si>
-    <t>knrl</t>
-  </si>
-  <si>
-    <t>Jafrac2</t>
-  </si>
-  <si>
-    <t>Dap160</t>
-  </si>
-  <si>
-    <t>prd</t>
-  </si>
-  <si>
-    <t>sll</t>
-  </si>
-  <si>
-    <t>rad50</t>
-  </si>
-  <si>
-    <t>Hs2st</t>
-  </si>
-  <si>
-    <t>spn-A</t>
-  </si>
-  <si>
-    <t>sgl</t>
-  </si>
-  <si>
-    <t>CadN</t>
-  </si>
-  <si>
-    <t>Dif</t>
-  </si>
-  <si>
-    <t>Taf4</t>
-  </si>
-  <si>
-    <t>CG1244</t>
-  </si>
-  <si>
-    <t>Crk</t>
-  </si>
-  <si>
-    <t>Glycogenin</t>
-  </si>
-  <si>
-    <t>ytr</t>
-  </si>
-  <si>
-    <t>Alk</t>
-  </si>
-  <si>
-    <t>sced</t>
-  </si>
-  <si>
-    <t>cin</t>
-  </si>
-  <si>
-    <t>l(2)gd1</t>
-  </si>
-  <si>
-    <t>l(2)gl</t>
-  </si>
-  <si>
-    <t>E(z)</t>
-  </si>
-  <si>
-    <t>kay</t>
-  </si>
-  <si>
-    <t>Dl</t>
-  </si>
-  <si>
-    <t>bigmax</t>
-  </si>
-  <si>
-    <t>amx</t>
-  </si>
-  <si>
-    <t>dib</t>
-  </si>
-  <si>
-    <t>form3</t>
-  </si>
-  <si>
-    <t>chif</t>
-  </si>
-  <si>
-    <t>bnb</t>
-  </si>
-  <si>
-    <t>chp</t>
-  </si>
-  <si>
-    <t>blow</t>
-  </si>
-  <si>
-    <t>ksr</t>
-  </si>
-  <si>
-    <t>Fas3</t>
-  </si>
-  <si>
-    <t>jagn</t>
-  </si>
-  <si>
-    <t>shrb</t>
-  </si>
-  <si>
-    <t>qua</t>
-  </si>
-  <si>
-    <t>E2f2</t>
-  </si>
-  <si>
-    <t>cact</t>
-  </si>
-  <si>
-    <t>Sur</t>
-  </si>
-  <si>
-    <t>l(2)efl</t>
-  </si>
-  <si>
-    <t>CG18369</t>
-  </si>
-  <si>
-    <t>hyx</t>
-  </si>
-  <si>
-    <t>Tab2</t>
-  </si>
-  <si>
-    <t>ALiX</t>
-  </si>
-  <si>
-    <t>Dat</t>
-  </si>
-  <si>
-    <t>dl</t>
-  </si>
-  <si>
-    <t>Mmp1</t>
-  </si>
-  <si>
-    <t>cathD</t>
-  </si>
-  <si>
-    <t>Mitf</t>
-  </si>
-  <si>
-    <t>Apc</t>
-  </si>
-  <si>
-    <t>Cks30A</t>
-  </si>
-  <si>
-    <t>PebIII</t>
-  </si>
-  <si>
-    <t>cta</t>
-  </si>
-  <si>
-    <t>CG12301</t>
-  </si>
-  <si>
-    <t>CG34417</t>
-  </si>
-  <si>
-    <t>Snap</t>
-  </si>
-  <si>
-    <t>chinmo</t>
-  </si>
-  <si>
-    <t>spir</t>
-  </si>
-  <si>
-    <t>gkt</t>
-  </si>
-  <si>
-    <t>MYPT-75D</t>
-  </si>
-  <si>
-    <t>Cyt-c-d</t>
-  </si>
-  <si>
-    <t>LanB1</t>
-  </si>
-  <si>
-    <t>toe</t>
-  </si>
-  <si>
-    <t>Chc</t>
-  </si>
-  <si>
-    <t>CG17221</t>
-  </si>
-  <si>
-    <t>Fmr1</t>
-  </si>
-  <si>
-    <t>trio</t>
-  </si>
-  <si>
-    <t>l(2)37Cc</t>
-  </si>
-  <si>
-    <t>dnc</t>
-  </si>
-  <si>
-    <t>Khc</t>
-  </si>
-  <si>
-    <t>CG9445</t>
-  </si>
-  <si>
-    <t>sls</t>
-  </si>
-  <si>
-    <t>Gtp-bp</t>
-  </si>
-  <si>
-    <t>emp</t>
-  </si>
-  <si>
-    <t>peb</t>
-  </si>
-  <si>
-    <t>CkIIalpha</t>
-  </si>
-  <si>
-    <t>siz</t>
-  </si>
-  <si>
-    <t>Mef2</t>
-  </si>
-  <si>
-    <t>Dcp-1</t>
-  </si>
-  <si>
-    <t>Iswi</t>
-  </si>
-  <si>
-    <t>dpld</t>
-  </si>
-  <si>
-    <t>eIF-4E</t>
-  </si>
-  <si>
-    <t>S6kII</t>
-  </si>
-  <si>
-    <t>Tak1</t>
-  </si>
-  <si>
-    <t>trc</t>
-  </si>
-  <si>
-    <t>dock</t>
-  </si>
-  <si>
-    <t>Pk92B</t>
-  </si>
-  <si>
-    <t>ics</t>
-  </si>
-  <si>
-    <t>ash1</t>
-  </si>
-  <si>
-    <t>Hr46</t>
-  </si>
-  <si>
-    <t>mbo</t>
-  </si>
-  <si>
-    <t>scrib</t>
-  </si>
-  <si>
-    <t>beta4GalNAcTA</t>
-  </si>
-  <si>
-    <t>sbb</t>
-  </si>
-  <si>
-    <t>G-ialpha65A</t>
-  </si>
-  <si>
-    <t>Pkn</t>
-  </si>
-  <si>
-    <t>svr</t>
-  </si>
-  <si>
-    <t>flfl</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>140up</t>
-  </si>
-  <si>
-    <t>stg</t>
-  </si>
-  <si>
-    <t>Lim1</t>
-  </si>
-  <si>
-    <t>up</t>
-  </si>
-  <si>
-    <t>esc</t>
-  </si>
-  <si>
-    <t>tok</t>
-  </si>
-  <si>
-    <t>kkv</t>
-  </si>
-  <si>
-    <t>ash2</t>
-  </si>
-  <si>
-    <t>sli</t>
-  </si>
-  <si>
-    <t>pot</t>
-  </si>
-  <si>
-    <t>dome</t>
-  </si>
-  <si>
-    <t>B4</t>
-  </si>
-  <si>
-    <t>run</t>
-  </si>
-  <si>
-    <t>caup</t>
-  </si>
-  <si>
-    <t>klar</t>
-  </si>
-  <si>
-    <t>rib</t>
-  </si>
-  <si>
-    <t>Pen</t>
-  </si>
-  <si>
-    <t>Pcaf</t>
-  </si>
-  <si>
-    <t>abd-A</t>
-  </si>
-  <si>
-    <t>disco</t>
-  </si>
-  <si>
-    <t>fd59A</t>
-  </si>
-  <si>
-    <t>Rab7</t>
-  </si>
-  <si>
-    <t>Ca-alpha1D</t>
-  </si>
-  <si>
-    <t>Rheb</t>
-  </si>
-  <si>
-    <t>stil</t>
-  </si>
-  <si>
-    <t>tutl</t>
-  </si>
-  <si>
-    <t>CG4500</t>
-  </si>
-  <si>
-    <t>inaC</t>
-  </si>
-  <si>
-    <t>E(bx)</t>
-  </si>
-  <si>
-    <t>ry</t>
-  </si>
-  <si>
-    <t>Idgf2</t>
-  </si>
-  <si>
-    <t>Vhl</t>
-  </si>
-  <si>
-    <t>pcm</t>
-  </si>
-  <si>
-    <t>NetB</t>
-  </si>
-  <si>
-    <t>Hmgs</t>
-  </si>
-  <si>
-    <t>sar1</t>
-  </si>
-  <si>
-    <t>Pgant35A</t>
-  </si>
-  <si>
-    <t>tum</t>
-  </si>
-  <si>
-    <t>Pi3K92E</t>
-  </si>
-  <si>
-    <t>noc</t>
-  </si>
-  <si>
-    <t>Jra</t>
-  </si>
-  <si>
-    <t>Dredd</t>
-  </si>
-  <si>
-    <t>grp</t>
-  </si>
-  <si>
-    <t>kuz</t>
-  </si>
-  <si>
-    <t>CG3987</t>
-  </si>
-  <si>
-    <t>Syx1A</t>
-  </si>
-  <si>
-    <t>pbl</t>
-  </si>
-  <si>
-    <t>BicD</t>
-  </si>
-  <si>
-    <t>ird5</t>
-  </si>
-  <si>
-    <t>Mbs</t>
-  </si>
-  <si>
-    <t>cos</t>
-  </si>
-  <si>
-    <t>ftz-f1</t>
-  </si>
-  <si>
-    <t>morgue</t>
-  </si>
-  <si>
-    <t>Rho1</t>
-  </si>
-  <si>
-    <t>inv</t>
-  </si>
-  <si>
-    <t>Borr</t>
-  </si>
-  <si>
-    <t>qm</t>
-  </si>
-  <si>
-    <t>RhoGAPp190</t>
-  </si>
-  <si>
-    <t>elav</t>
-  </si>
-  <si>
-    <t>mth</t>
-  </si>
-  <si>
-    <t>btl</t>
-  </si>
-  <si>
-    <t>fax</t>
-  </si>
-  <si>
-    <t>NAT1</t>
-  </si>
-  <si>
-    <t>cbt</t>
-  </si>
-  <si>
-    <t>ninaE</t>
-  </si>
-  <si>
-    <t>CG34379</t>
-  </si>
-  <si>
-    <t>par-1</t>
-  </si>
-  <si>
-    <t>Atpalpha</t>
-  </si>
-  <si>
-    <t>esg</t>
-  </si>
-  <si>
-    <t>fl(2)d</t>
-  </si>
-  <si>
-    <t>E2f</t>
-  </si>
-  <si>
-    <t>Mkp3</t>
-  </si>
-  <si>
-    <t>Pak</t>
-  </si>
-  <si>
-    <t>dsf</t>
-  </si>
-  <si>
-    <t>mmy</t>
-  </si>
-  <si>
-    <t>Eip71CD</t>
-  </si>
-  <si>
-    <t>msk</t>
-  </si>
-  <si>
-    <t>Atg5</t>
-  </si>
-  <si>
-    <t>Ggamma1</t>
-  </si>
-  <si>
-    <t>ImpE3</t>
-  </si>
-  <si>
-    <t>Akt1</t>
-  </si>
-  <si>
-    <t>ix</t>
-  </si>
-  <si>
-    <t>tud</t>
-  </si>
-  <si>
-    <t>Caf1</t>
-  </si>
-  <si>
-    <t>Mer</t>
-  </si>
-  <si>
-    <t>glu</t>
-  </si>
-  <si>
-    <t>Stat92E</t>
-  </si>
-  <si>
-    <t>thr</t>
-  </si>
-  <si>
-    <t>dup</t>
-  </si>
-  <si>
-    <t>tou</t>
-  </si>
-  <si>
-    <t>cp309</t>
-  </si>
-  <si>
-    <t>qkr58E-3</t>
-  </si>
-  <si>
-    <t>Bap60</t>
-  </si>
-  <si>
-    <t>snf</t>
-  </si>
-  <si>
-    <t>dlg1</t>
-  </si>
-  <si>
-    <t>Arc42</t>
-  </si>
-  <si>
-    <t>Mtl</t>
-  </si>
-  <si>
-    <t>Oseg1</t>
-  </si>
-  <si>
-    <t>CG2681</t>
-  </si>
-  <si>
-    <t>MED24</t>
-  </si>
-  <si>
-    <t>Pvf1</t>
-  </si>
-  <si>
-    <t>Src64B</t>
-  </si>
-  <si>
-    <t>CG6372</t>
-  </si>
-  <si>
-    <t>sns</t>
-  </si>
-  <si>
-    <t>dei</t>
-  </si>
-  <si>
-    <t>nej</t>
-  </si>
-  <si>
-    <t>msn</t>
-  </si>
-  <si>
-    <t>Ef1gamma</t>
-  </si>
-  <si>
-    <t>hyd</t>
-  </si>
-  <si>
-    <t>Sulf1</t>
-  </si>
-  <si>
-    <t>Lac</t>
-  </si>
-  <si>
-    <t>sax</t>
-  </si>
-  <si>
-    <t>chic</t>
-  </si>
-  <si>
-    <t>Arp66B</t>
-  </si>
-  <si>
-    <t>tamo</t>
-  </si>
-  <si>
-    <t>boss</t>
-  </si>
-  <si>
-    <t>ssh</t>
-  </si>
-  <si>
-    <t>ecd</t>
-  </si>
-  <si>
-    <t>Trl</t>
-  </si>
-  <si>
-    <t>Dad</t>
-  </si>
-  <si>
-    <t>Mmp2</t>
-  </si>
-  <si>
-    <t>foxo</t>
-  </si>
-  <si>
-    <t>sgg</t>
-  </si>
-  <si>
-    <t>Ephrin</t>
-  </si>
-  <si>
     <t>CG33205</t>
   </si>
   <si>
     <t>EcR</t>
-  </si>
-  <si>
-    <t>by</t>
-  </si>
-  <si>
-    <t>tld</t>
-  </si>
-  <si>
-    <t>sas</t>
-  </si>
-  <si>
-    <t>her</t>
-  </si>
-  <si>
-    <t>CG9509</t>
-  </si>
-  <si>
-    <t>Cyp1</t>
-  </si>
-  <si>
-    <t>ap</t>
-  </si>
-  <si>
-    <t>crc</t>
-  </si>
-  <si>
-    <t>bap</t>
-  </si>
-  <si>
-    <t>tsh</t>
-  </si>
-  <si>
-    <t>Traf6</t>
-  </si>
-  <si>
-    <t>msi</t>
-  </si>
-  <si>
-    <t>CG32486</t>
-  </si>
-  <si>
-    <t>Krn</t>
-  </si>
-  <si>
-    <t>CtBP</t>
-  </si>
-  <si>
-    <t>Antp</t>
-  </si>
-  <si>
-    <t>Set2</t>
-  </si>
-  <si>
-    <t>RhoL</t>
-  </si>
-  <si>
-    <t>bcd</t>
-  </si>
-  <si>
-    <t>Syb</t>
-  </si>
-  <si>
-    <t>dom</t>
-  </si>
-  <si>
-    <t>Not1</t>
-  </si>
-  <si>
-    <t>Abl</t>
-  </si>
-  <si>
-    <t>oaf</t>
-  </si>
-  <si>
-    <t>yrt</t>
-  </si>
-  <si>
-    <t>Ank2</t>
-  </si>
-  <si>
-    <t>mus304</t>
-  </si>
-  <si>
-    <t>CSN4</t>
-  </si>
-  <si>
-    <t>how</t>
-  </si>
-  <si>
-    <t>Mhc</t>
-  </si>
-  <si>
-    <t>cbx</t>
-  </si>
-  <si>
-    <t>exu</t>
-  </si>
-  <si>
-    <t>da</t>
-  </si>
-  <si>
-    <t>CG2678</t>
-  </si>
-  <si>
-    <t>dos</t>
-  </si>
-  <si>
-    <t>brk</t>
-  </si>
-  <si>
-    <t>CG6416</t>
-  </si>
-  <si>
-    <t>jar</t>
-  </si>
-  <si>
-    <t>RhoGAP68F</t>
-  </si>
-  <si>
-    <t>trn</t>
-  </si>
-  <si>
-    <t>d4</t>
-  </si>
-  <si>
-    <t>Tm1</t>
-  </si>
-  <si>
-    <t>mam</t>
-  </si>
-  <si>
-    <t>Sema-2a</t>
-  </si>
-  <si>
-    <t>fal</t>
-  </si>
-  <si>
-    <t>ena</t>
-  </si>
-  <si>
-    <t>Axn</t>
-  </si>
-  <si>
-    <t>loco</t>
-  </si>
-  <si>
-    <t>santa-maria</t>
-  </si>
-  <si>
-    <t>shot</t>
-  </si>
-  <si>
-    <t>emc</t>
-  </si>
-  <si>
-    <t>sw</t>
-  </si>
-  <si>
-    <t>bhr</t>
-  </si>
-  <si>
-    <t>gl</t>
-  </si>
-  <si>
-    <t>drm</t>
-  </si>
-  <si>
-    <t>betaTub56D</t>
-  </si>
-  <si>
-    <t>mask</t>
-  </si>
-  <si>
-    <t>CG17739</t>
-  </si>
-  <si>
-    <t>ttk</t>
-  </si>
-  <si>
-    <t>pyd</t>
-  </si>
-  <si>
-    <t>odd</t>
-  </si>
-  <si>
-    <t>Prm</t>
-  </si>
-  <si>
-    <t>Mlc1</t>
-  </si>
-  <si>
-    <t>th</t>
-  </si>
-  <si>
-    <t>wls</t>
-  </si>
-  <si>
-    <t>RpL30</t>
-  </si>
-  <si>
-    <t>dsd</t>
-  </si>
-  <si>
-    <t>cas</t>
-  </si>
-  <si>
-    <t>fw</t>
-  </si>
-  <si>
-    <t>Spred</t>
-  </si>
-  <si>
-    <t>wg</t>
-  </si>
-  <si>
-    <t>yellow-f</t>
-  </si>
-  <si>
-    <t>Vps28</t>
-  </si>
-  <si>
-    <t>bs</t>
-  </si>
-  <si>
-    <t>MED4</t>
-  </si>
-  <si>
-    <t>CG13850</t>
-  </si>
-  <si>
-    <t>dpp</t>
-  </si>
-  <si>
-    <t>brat</t>
-  </si>
-  <si>
-    <t>rhea</t>
-  </si>
-  <si>
-    <t>Myo61F</t>
-  </si>
-  <si>
-    <t>hpo</t>
-  </si>
-  <si>
-    <t>CG3075</t>
-  </si>
-  <si>
-    <t>cnk</t>
-  </si>
-  <si>
-    <t>dec-1</t>
-  </si>
-  <si>
-    <t>nmo</t>
-  </si>
-  <si>
-    <t>Lar</t>
-  </si>
-  <si>
-    <t>pdm2</t>
-  </si>
-  <si>
-    <t>Sxl</t>
-  </si>
-  <si>
-    <t>SelG</t>
-  </si>
-  <si>
-    <t>Su(z)12</t>
-  </si>
-  <si>
-    <t>LanB2</t>
-  </si>
-  <si>
-    <t>Atg6</t>
-  </si>
-  <si>
-    <t>hkl</t>
-  </si>
-  <si>
-    <t>Hs6st</t>
-  </si>
-  <si>
-    <t>Sema-1b</t>
-  </si>
-  <si>
-    <t>tup</t>
-  </si>
-  <si>
-    <t>alpha-Spec</t>
   </si>
 </sst>
 </file>
@@ -1776,7 +1827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B537"/>
+  <dimension ref="A1:B543"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1813,87 +1864,87 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
         <v>28</v>
@@ -1917,1495 +1968,1495 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" t="s">
         <v>33</v>
-      </c>
-      <c r="B18" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
         <v>35</v>
-      </c>
-      <c r="B19" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" t="s">
         <v>37</v>
-      </c>
-      <c r="B20" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" t="s">
         <v>39</v>
-      </c>
-      <c r="B21" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" t="s">
         <v>41</v>
-      </c>
-      <c r="B22" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" t="s">
         <v>43</v>
-      </c>
-      <c r="B23" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" t="s">
         <v>45</v>
-      </c>
-      <c r="B24" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B28" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B31" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B33" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B34" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B36" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B40" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B41" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B43" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B44" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B45" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B46" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B47" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B48" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B49" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B50" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B51" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B52" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B53" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B54" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B55" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="B56" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B57" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B58" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B59" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B60" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>115</v>
+        <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B62" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B64" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B65" t="s">
-        <v>4</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>18</v>
+        <v>115</v>
       </c>
       <c r="B66" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B67" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="B68" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>2</v>
+        <v>121</v>
       </c>
       <c r="B69" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B70" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B71" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="B72" t="s">
-        <v>19</v>
+        <v>128</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>133</v>
+        <v>5</v>
       </c>
       <c r="B73" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B74" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B75" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B76" t="s">
-        <v>29</v>
+        <v>135</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="B77" t="s">
-        <v>89</v>
+        <v>136</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B78" t="s">
-        <v>140</v>
+        <v>26</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="B79" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="B80" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B81" t="s">
-        <v>144</v>
+        <v>103</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B82" t="s">
-        <v>125</v>
+        <v>53</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B83" t="s">
-        <v>147</v>
+        <v>95</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B84" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B85" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B86" t="s">
-        <v>152</v>
+        <v>102</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B87" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B88" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B89" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="B90" t="s">
-        <v>158</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>159</v>
+        <v>115</v>
       </c>
       <c r="B91" t="s">
-        <v>23</v>
+        <v>155</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B92" t="s">
-        <v>85</v>
+        <v>157</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>113</v>
+        <v>158</v>
       </c>
       <c r="B93" t="s">
-        <v>161</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>162</v>
+        <v>21</v>
       </c>
       <c r="B94" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B95" t="s">
-        <v>165</v>
+        <v>120</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>166</v>
+        <v>34</v>
       </c>
       <c r="B96" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B97" t="s">
-        <v>69</v>
+        <v>162</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B98" t="s">
-        <v>124</v>
+        <v>164</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B99" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="B100" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B101" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>174</v>
+        <v>29</v>
       </c>
       <c r="B102" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>86</v>
+        <v>170</v>
       </c>
       <c r="B103" t="s">
-        <v>175</v>
+        <v>113</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B104" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="B105" t="s">
-        <v>87</v>
+        <v>174</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B106" t="s">
-        <v>111</v>
+        <v>176</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B107" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>181</v>
+        <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>182</v>
+        <v>57</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B109" t="s">
-        <v>60</v>
+        <v>180</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>184</v>
+        <v>56</v>
       </c>
       <c r="B110" t="s">
-        <v>185</v>
+        <v>67</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B111" t="s">
-        <v>142</v>
+        <v>182</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B112" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B113" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>92</v>
+        <v>186</v>
       </c>
       <c r="B114" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>180</v>
+        <v>57</v>
       </c>
       <c r="B115" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>193</v>
+        <v>62</v>
       </c>
       <c r="B116" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>195</v>
+        <v>48</v>
       </c>
       <c r="B117" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B118" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="B119" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B120" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="B121" t="s">
-        <v>204</v>
+        <v>149</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>85</v>
+        <v>197</v>
       </c>
       <c r="B122" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="B123" t="s">
-        <v>207</v>
+        <v>114</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="B124" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="B125" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>212</v>
+        <v>53</v>
       </c>
       <c r="B126" t="s">
-        <v>17</v>
+        <v>203</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>151</v>
+        <v>204</v>
       </c>
       <c r="B127" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>209</v>
+        <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>213</v>
+        <v>47</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B129" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>215</v>
+        <v>145</v>
       </c>
       <c r="B130" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>96</v>
+        <v>154</v>
       </c>
       <c r="B131" t="s">
-        <v>217</v>
+        <v>74</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="B132" t="s">
-        <v>129</v>
+        <v>210</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B133" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>221</v>
+        <v>30</v>
       </c>
       <c r="B134" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>42</v>
+        <v>213</v>
       </c>
       <c r="B135" t="s">
-        <v>8</v>
+        <v>214</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B136" t="s">
-        <v>208</v>
+        <v>53</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>138</v>
+        <v>216</v>
       </c>
       <c r="B137" t="s">
-        <v>158</v>
+        <v>217</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B138" t="s">
-        <v>91</v>
+        <v>219</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="B139" t="s">
-        <v>37</v>
+        <v>220</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>220</v>
+        <v>103</v>
       </c>
       <c r="B140" t="s">
-        <v>202</v>
+        <v>143</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>214</v>
+        <v>49</v>
       </c>
       <c r="B141" t="s">
-        <v>226</v>
+        <v>57</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="B142" t="s">
-        <v>227</v>
+        <v>102</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B143" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B144" t="s">
-        <v>180</v>
+        <v>224</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>231</v>
+        <v>161</v>
       </c>
       <c r="B145" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B146" t="s">
-        <v>24</v>
+        <v>172</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>234</v>
+        <v>163</v>
       </c>
       <c r="B147" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>236</v>
+        <v>65</v>
       </c>
       <c r="B148" t="s">
-        <v>237</v>
+        <v>26</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>238</v>
+        <v>127</v>
       </c>
       <c r="B149" t="s">
-        <v>46</v>
+        <v>228</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>157</v>
+        <v>229</v>
       </c>
       <c r="B150" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="B151" t="s">
-        <v>241</v>
+        <v>174</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>242</v>
+        <v>158</v>
       </c>
       <c r="B152" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="B153" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="B154" t="s">
-        <v>247</v>
+        <v>52</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>74</v>
+        <v>236</v>
       </c>
       <c r="B155" t="s">
-        <v>179</v>
+        <v>237</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="B156" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="B157" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>200</v>
+        <v>242</v>
       </c>
       <c r="B158" t="s">
-        <v>252</v>
+        <v>52</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>100</v>
+        <v>243</v>
       </c>
       <c r="B159" t="s">
-        <v>253</v>
+        <v>13</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>11</v>
+        <v>244</v>
       </c>
       <c r="B160" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="B161" t="s">
-        <v>108</v>
+        <v>16</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>256</v>
+        <v>145</v>
       </c>
       <c r="B162" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="B163" t="s">
-        <v>259</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>260</v>
+        <v>158</v>
       </c>
       <c r="B164" t="s">
-        <v>261</v>
+        <v>162</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B165" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="B166" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>265</v>
+        <v>226</v>
       </c>
       <c r="B167" t="s">
-        <v>193</v>
+        <v>252</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>266</v>
+        <v>53</v>
       </c>
       <c r="B168" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="B169" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="B170" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B171" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="B172" t="s">
-        <v>91</v>
+        <v>258</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>75</v>
+        <v>259</v>
       </c>
       <c r="B173" t="s">
-        <v>19</v>
+        <v>260</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>102</v>
+        <v>261</v>
       </c>
       <c r="B174" t="s">
-        <v>187</v>
+        <v>53</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>63</v>
+        <v>262</v>
       </c>
       <c r="B175" t="s">
-        <v>68</v>
+        <v>263</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="B176" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>272</v>
+        <v>30</v>
       </c>
       <c r="B177" t="s">
-        <v>273</v>
+        <v>102</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="B178" t="s">
-        <v>133</v>
+        <v>260</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>114</v>
+        <v>266</v>
       </c>
       <c r="B179" t="s">
-        <v>39</v>
+        <v>204</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="B180" t="s">
-        <v>7</v>
+        <v>267</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
-        <v>173</v>
+        <v>111</v>
       </c>
       <c r="B181" t="s">
-        <v>19</v>
+        <v>268</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="B182" t="s">
-        <v>182</v>
+        <v>270</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" t="s">
-        <v>236</v>
+        <v>40</v>
       </c>
       <c r="B183" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B184" t="s">
-        <v>40</v>
+        <v>271</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B185" t="s">
-        <v>278</v>
+        <v>32</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" t="s">
-        <v>155</v>
+        <v>273</v>
       </c>
       <c r="B186" t="s">
-        <v>279</v>
+        <v>236</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" t="s">
-        <v>67</v>
+        <v>167</v>
       </c>
       <c r="B187" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B188" t="s">
-        <v>281</v>
+        <v>52</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" t="s">
-        <v>282</v>
+        <v>228</v>
       </c>
       <c r="B189" t="s">
-        <v>283</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="B190" t="s">
-        <v>285</v>
+        <v>148</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" t="s">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="B191" t="s">
-        <v>197</v>
+        <v>131</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" t="s">
-        <v>210</v>
+        <v>277</v>
       </c>
       <c r="B192" t="s">
-        <v>239</v>
+        <v>20</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" t="s">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="B193" t="s">
-        <v>86</v>
+        <v>278</v>
       </c>
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B194" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195" t="s">
-        <v>171</v>
+        <v>281</v>
       </c>
       <c r="B195" t="s">
-        <v>146</v>
+        <v>282</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" t="s">
-        <v>288</v>
+        <v>213</v>
       </c>
       <c r="B196" t="s">
-        <v>289</v>
+        <v>57</v>
       </c>
     </row>
     <row r="197" spans="1:2">
       <c r="A197" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="B197" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B198" t="s">
-        <v>245</v>
+        <v>285</v>
       </c>
     </row>
     <row r="199" spans="1:2">
       <c r="A199" t="s">
-        <v>228</v>
+        <v>180</v>
       </c>
       <c r="B199" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="200" spans="1:2">
       <c r="A200" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="B200" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201" t="s">
-        <v>251</v>
+        <v>104</v>
       </c>
       <c r="B201" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
-        <v>221</v>
+        <v>288</v>
       </c>
       <c r="B202" t="s">
-        <v>30</v>
+        <v>289</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B203" t="s">
-        <v>55</v>
+        <v>113</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" t="s">
-        <v>295</v>
+        <v>110</v>
       </c>
       <c r="B204" t="s">
         <v>109</v>
@@ -3413,423 +3464,423 @@
     </row>
     <row r="205" spans="1:2">
       <c r="A205" t="s">
-        <v>168</v>
+        <v>219</v>
       </c>
       <c r="B205" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="206" spans="1:2">
       <c r="A206" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B206" t="s">
-        <v>298</v>
+        <v>149</v>
       </c>
     </row>
     <row r="207" spans="1:2">
       <c r="A207" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B207" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208" t="s">
-        <v>155</v>
+        <v>294</v>
       </c>
       <c r="B208" t="s">
-        <v>260</v>
+        <v>149</v>
       </c>
     </row>
     <row r="209" spans="1:2">
       <c r="A209" t="s">
-        <v>56</v>
+        <v>176</v>
       </c>
       <c r="B209" t="s">
-        <v>156</v>
+        <v>295</v>
       </c>
     </row>
     <row r="210" spans="1:2">
       <c r="A210" t="s">
-        <v>33</v>
+        <v>296</v>
       </c>
       <c r="B210" t="s">
-        <v>243</v>
+        <v>183</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B211" t="s">
-        <v>301</v>
+        <v>27</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212" t="s">
-        <v>15</v>
+        <v>298</v>
       </c>
       <c r="B212" t="s">
-        <v>90</v>
+        <v>154</v>
       </c>
     </row>
     <row r="213" spans="1:2">
       <c r="A213" t="s">
-        <v>302</v>
+        <v>63</v>
       </c>
       <c r="B213" t="s">
-        <v>303</v>
+        <v>88</v>
       </c>
     </row>
     <row r="214" spans="1:2">
       <c r="A214" t="s">
-        <v>259</v>
+        <v>299</v>
       </c>
       <c r="B214" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="215" spans="1:2">
       <c r="A215" t="s">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="B215" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="216" spans="1:2">
       <c r="A216" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B216" t="s">
-        <v>307</v>
+        <v>90</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
-        <v>136</v>
+        <v>199</v>
       </c>
       <c r="B217" t="s">
-        <v>235</v>
+        <v>260</v>
       </c>
     </row>
     <row r="218" spans="1:2">
       <c r="A218" t="s">
-        <v>308</v>
+        <v>121</v>
       </c>
       <c r="B218" t="s">
-        <v>42</v>
+        <v>303</v>
       </c>
     </row>
     <row r="219" spans="1:2">
       <c r="A219" t="s">
-        <v>200</v>
+        <v>304</v>
       </c>
       <c r="B219" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" t="s">
-        <v>189</v>
+        <v>306</v>
       </c>
       <c r="B220" t="s">
-        <v>152</v>
+        <v>307</v>
       </c>
     </row>
     <row r="221" spans="1:2">
       <c r="A221" t="s">
-        <v>310</v>
+        <v>96</v>
       </c>
       <c r="B221" t="s">
-        <v>311</v>
+        <v>106</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B222" t="s">
-        <v>104</v>
+        <v>307</v>
       </c>
     </row>
     <row r="223" spans="1:2">
       <c r="A223" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
       <c r="B223" t="s">
-        <v>204</v>
+        <v>239</v>
       </c>
     </row>
     <row r="224" spans="1:2">
       <c r="A224" t="s">
-        <v>313</v>
+        <v>115</v>
       </c>
       <c r="B224" t="s">
-        <v>160</v>
+        <v>310</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>189</v>
+        <v>253</v>
       </c>
       <c r="B225" t="s">
-        <v>314</v>
+        <v>91</v>
       </c>
     </row>
     <row r="226" spans="1:2">
       <c r="A226" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B226" t="s">
-        <v>316</v>
+        <v>177</v>
       </c>
     </row>
     <row r="227" spans="1:2">
       <c r="A227" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B227" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
     </row>
     <row r="228" spans="1:2">
       <c r="A228" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="B228" t="s">
-        <v>97</v>
+        <v>214</v>
       </c>
     </row>
     <row r="229" spans="1:2">
       <c r="A229" t="s">
-        <v>318</v>
+        <v>259</v>
       </c>
       <c r="B229" t="s">
-        <v>153</v>
+        <v>313</v>
       </c>
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
-        <v>47</v>
+        <v>314</v>
       </c>
       <c r="B230" t="s">
-        <v>88</v>
+        <v>315</v>
       </c>
     </row>
     <row r="231" spans="1:2">
       <c r="A231" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="B231" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="232" spans="1:2">
       <c r="A232" t="s">
-        <v>320</v>
+        <v>30</v>
       </c>
       <c r="B232" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>314</v>
+        <v>149</v>
       </c>
       <c r="B233" t="s">
-        <v>322</v>
+        <v>184</v>
       </c>
     </row>
     <row r="234" spans="1:2">
       <c r="A234" t="s">
-        <v>279</v>
+        <v>198</v>
       </c>
       <c r="B234" t="s">
-        <v>89</v>
+        <v>161</v>
       </c>
     </row>
     <row r="235" spans="1:2">
       <c r="A235" t="s">
-        <v>323</v>
+        <v>27</v>
       </c>
       <c r="B235" t="s">
-        <v>324</v>
+        <v>27</v>
       </c>
     </row>
     <row r="236" spans="1:2">
       <c r="A236" t="s">
-        <v>40</v>
+        <v>318</v>
       </c>
       <c r="B236" t="s">
-        <v>189</v>
+        <v>319</v>
       </c>
     </row>
     <row r="237" spans="1:2">
       <c r="A237" t="s">
-        <v>325</v>
+        <v>257</v>
       </c>
       <c r="B237" t="s">
-        <v>101</v>
+        <v>320</v>
       </c>
     </row>
     <row r="238" spans="1:2">
       <c r="A238" t="s">
-        <v>326</v>
+        <v>182</v>
       </c>
       <c r="B238" t="s">
-        <v>170</v>
+        <v>321</v>
       </c>
     </row>
     <row r="239" spans="1:2">
       <c r="A239" t="s">
+        <v>151</v>
+      </c>
+      <c r="B239" t="s">
         <v>96</v>
-      </c>
-      <c r="B239" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B240" t="s">
-        <v>317</v>
+        <v>158</v>
       </c>
     </row>
     <row r="241" spans="1:2">
       <c r="A241" t="s">
-        <v>329</v>
+        <v>231</v>
       </c>
       <c r="B241" t="s">
-        <v>330</v>
+        <v>227</v>
       </c>
     </row>
     <row r="242" spans="1:2">
       <c r="A242" t="s">
-        <v>273</v>
+        <v>323</v>
       </c>
       <c r="B242" t="s">
-        <v>126</v>
+        <v>324</v>
       </c>
     </row>
     <row r="243" spans="1:2">
       <c r="A243" t="s">
-        <v>256</v>
+        <v>190</v>
       </c>
       <c r="B243" t="s">
-        <v>331</v>
+        <v>190</v>
       </c>
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>332</v>
+        <v>123</v>
       </c>
       <c r="B244" t="s">
-        <v>79</v>
+        <v>325</v>
       </c>
     </row>
     <row r="245" spans="1:2">
       <c r="A245" t="s">
-        <v>44</v>
+        <v>272</v>
       </c>
       <c r="B245" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
     </row>
     <row r="246" spans="1:2">
       <c r="A246" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="B246" t="s">
-        <v>58</v>
+        <v>328</v>
       </c>
     </row>
     <row r="247" spans="1:2">
       <c r="A247" t="s">
-        <v>233</v>
+        <v>329</v>
       </c>
       <c r="B247" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
     </row>
     <row r="248" spans="1:2">
       <c r="A248" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B248" t="s">
-        <v>209</v>
+        <v>319</v>
       </c>
     </row>
     <row r="249" spans="1:2">
       <c r="A249" t="s">
-        <v>122</v>
+        <v>5</v>
       </c>
       <c r="B249" t="s">
-        <v>293</v>
+        <v>331</v>
       </c>
     </row>
     <row r="250" spans="1:2">
       <c r="A250" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B250" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
     </row>
     <row r="251" spans="1:2">
       <c r="A251" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B251" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
     </row>
     <row r="252" spans="1:2">
       <c r="A252" t="s">
-        <v>72</v>
+        <v>193</v>
       </c>
       <c r="B252" t="s">
-        <v>337</v>
+        <v>87</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>338</v>
+        <v>291</v>
       </c>
       <c r="B253" t="s">
-        <v>337</v>
+        <v>56</v>
       </c>
     </row>
     <row r="254" spans="1:2">
       <c r="A254" t="s">
-        <v>339</v>
+        <v>120</v>
       </c>
       <c r="B254" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
-        <v>141</v>
+        <v>334</v>
       </c>
       <c r="B255" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>53</v>
+        <v>236</v>
       </c>
       <c r="B256" t="s">
-        <v>337</v>
+        <v>214</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" t="s">
-        <v>177</v>
+        <v>336</v>
       </c>
       <c r="B257" t="s">
         <v>337</v>
@@ -3837,50 +3888,50 @@
     </row>
     <row r="258" spans="1:2">
       <c r="A258" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="B258" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" t="s">
-        <v>54</v>
+        <v>209</v>
       </c>
       <c r="B259" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="260" spans="1:2">
       <c r="A260" t="s">
-        <v>175</v>
+        <v>99</v>
       </c>
       <c r="B260" t="s">
-        <v>337</v>
+        <v>214</v>
       </c>
     </row>
     <row r="261" spans="1:2">
       <c r="A261" t="s">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="B261" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
     </row>
     <row r="262" spans="1:2">
       <c r="A262" t="s">
+        <v>340</v>
+      </c>
+      <c r="B262" t="s">
         <v>341</v>
-      </c>
-      <c r="B262" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="263" spans="1:2">
       <c r="A263" t="s">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="B263" t="s">
-        <v>337</v>
+        <v>166</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -3888,1511 +3939,1511 @@
         <v>342</v>
       </c>
       <c r="B264" t="s">
-        <v>296</v>
+        <v>145</v>
       </c>
     </row>
     <row r="265" spans="1:2">
       <c r="A265" t="s">
-        <v>243</v>
+        <v>100</v>
       </c>
       <c r="B265" t="s">
-        <v>296</v>
+        <v>16</v>
       </c>
     </row>
     <row r="266" spans="1:2">
       <c r="A266" t="s">
-        <v>52</v>
+        <v>343</v>
       </c>
       <c r="B266" t="s">
-        <v>343</v>
+        <v>281</v>
       </c>
     </row>
     <row r="267" spans="1:2">
       <c r="A267" t="s">
-        <v>344</v>
+        <v>302</v>
       </c>
       <c r="B267" t="s">
-        <v>343</v>
+        <v>249</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" t="s">
-        <v>268</v>
+        <v>300</v>
       </c>
       <c r="B268" t="s">
-        <v>70</v>
+        <v>306</v>
       </c>
     </row>
     <row r="269" spans="1:2">
       <c r="A269" t="s">
-        <v>223</v>
+        <v>158</v>
       </c>
       <c r="B269" t="s">
-        <v>70</v>
+        <v>200</v>
       </c>
     </row>
     <row r="270" spans="1:2">
       <c r="A270" t="s">
-        <v>345</v>
+        <v>103</v>
       </c>
       <c r="B270" t="s">
-        <v>78</v>
+        <v>177</v>
       </c>
     </row>
     <row r="271" spans="1:2">
       <c r="A271" t="s">
-        <v>192</v>
+        <v>44</v>
       </c>
       <c r="B271" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B272" t="s">
-        <v>347</v>
+        <v>293</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" t="s">
-        <v>342</v>
+        <v>246</v>
       </c>
       <c r="B273" t="s">
-        <v>3</v>
+        <v>331</v>
       </c>
     </row>
     <row r="274" spans="1:2">
       <c r="A274" t="s">
-        <v>348</v>
+        <v>247</v>
       </c>
       <c r="B274" t="s">
-        <v>3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="275" spans="1:2">
       <c r="A275" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
       <c r="B275" t="s">
-        <v>234</v>
+        <v>173</v>
       </c>
     </row>
     <row r="276" spans="1:2">
       <c r="A276" t="s">
-        <v>322</v>
+        <v>183</v>
       </c>
       <c r="B276" t="s">
-        <v>349</v>
+        <v>85</v>
       </c>
     </row>
     <row r="277" spans="1:2">
       <c r="A277" t="s">
-        <v>2</v>
+        <v>344</v>
       </c>
       <c r="B277" t="s">
-        <v>350</v>
+        <v>324</v>
       </c>
     </row>
     <row r="278" spans="1:2">
       <c r="A278" t="s">
-        <v>351</v>
+        <v>295</v>
       </c>
       <c r="B278" t="s">
-        <v>313</v>
+        <v>345</v>
       </c>
     </row>
     <row r="279" spans="1:2">
       <c r="A279" t="s">
-        <v>131</v>
+        <v>346</v>
       </c>
       <c r="B279" t="s">
-        <v>247</v>
+        <v>347</v>
       </c>
     </row>
     <row r="280" spans="1:2">
       <c r="A280" t="s">
-        <v>352</v>
+        <v>131</v>
       </c>
       <c r="B280" t="s">
-        <v>190</v>
+        <v>348</v>
       </c>
     </row>
     <row r="281" spans="1:2">
       <c r="A281" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B281" t="s">
-        <v>124</v>
+        <v>340</v>
       </c>
     </row>
     <row r="282" spans="1:2">
       <c r="A282" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B282" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="283" spans="1:2">
       <c r="A283" t="s">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="B283" t="s">
-        <v>99</v>
+        <v>352</v>
       </c>
     </row>
     <row r="284" spans="1:2">
       <c r="A284" t="s">
-        <v>106</v>
+        <v>300</v>
       </c>
       <c r="B284" t="s">
-        <v>19</v>
+        <v>290</v>
       </c>
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>274</v>
+        <v>327</v>
       </c>
       <c r="B285" t="s">
-        <v>101</v>
+        <v>319</v>
       </c>
     </row>
     <row r="286" spans="1:2">
       <c r="A286" t="s">
-        <v>180</v>
+        <v>33</v>
       </c>
       <c r="B286" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="287" spans="1:2">
       <c r="A287" t="s">
-        <v>356</v>
+        <v>327</v>
       </c>
       <c r="B287" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="288" spans="1:2">
       <c r="A288" t="s">
-        <v>358</v>
+        <v>223</v>
       </c>
       <c r="B288" t="s">
-        <v>294</v>
+        <v>355</v>
       </c>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" t="s">
-        <v>220</v>
+        <v>356</v>
       </c>
       <c r="B289" t="s">
-        <v>190</v>
+        <v>357</v>
       </c>
     </row>
     <row r="290" spans="1:2">
       <c r="A290" t="s">
+        <v>358</v>
+      </c>
+      <c r="B290" t="s">
         <v>359</v>
-      </c>
-      <c r="B290" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="291" spans="1:2">
       <c r="A291" t="s">
-        <v>317</v>
+        <v>360</v>
       </c>
       <c r="B291" t="s">
-        <v>195</v>
+        <v>240</v>
       </c>
     </row>
     <row r="292" spans="1:2">
       <c r="A292" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="B292" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="293" spans="1:2">
       <c r="A293" t="s">
-        <v>35</v>
+        <v>363</v>
       </c>
       <c r="B293" t="s">
-        <v>361</v>
+        <v>297</v>
       </c>
     </row>
     <row r="294" spans="1:2">
       <c r="A294" t="s">
-        <v>202</v>
+        <v>287</v>
       </c>
       <c r="B294" t="s">
-        <v>333</v>
+        <v>12</v>
       </c>
     </row>
     <row r="295" spans="1:2">
       <c r="A295" t="s">
-        <v>362</v>
+        <v>50</v>
       </c>
       <c r="B295" t="s">
-        <v>168</v>
+        <v>364</v>
       </c>
     </row>
     <row r="296" spans="1:2">
       <c r="A296" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B296" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="297" spans="1:2">
       <c r="A297" t="s">
-        <v>365</v>
+        <v>132</v>
       </c>
       <c r="B297" t="s">
-        <v>366</v>
+        <v>147</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
-        <v>355</v>
+        <v>130</v>
       </c>
       <c r="B298" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="299" spans="1:2">
       <c r="A299" t="s">
+        <v>367</v>
+      </c>
+      <c r="B299" t="s">
         <v>368</v>
-      </c>
-      <c r="B299" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="300" spans="1:2">
       <c r="A300" t="s">
+        <v>369</v>
+      </c>
+      <c r="B300" t="s">
         <v>370</v>
-      </c>
-      <c r="B300" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="301" spans="1:2">
       <c r="A301" t="s">
-        <v>307</v>
+        <v>149</v>
       </c>
       <c r="B301" t="s">
-        <v>37</v>
+        <v>371</v>
       </c>
     </row>
     <row r="302" spans="1:2">
       <c r="A302" t="s">
-        <v>371</v>
+        <v>249</v>
       </c>
       <c r="B302" t="s">
-        <v>277</v>
+        <v>158</v>
       </c>
     </row>
     <row r="303" spans="1:2">
       <c r="A303" t="s">
-        <v>372</v>
+        <v>138</v>
       </c>
       <c r="B303" t="s">
-        <v>104</v>
+        <v>203</v>
       </c>
     </row>
     <row r="304" spans="1:2">
       <c r="A304" t="s">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="B304" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="305" spans="1:2">
       <c r="A305" t="s">
-        <v>61</v>
+        <v>204</v>
       </c>
       <c r="B305" t="s">
-        <v>374</v>
+        <v>91</v>
       </c>
     </row>
     <row r="306" spans="1:2">
       <c r="A306" t="s">
-        <v>168</v>
+        <v>78</v>
       </c>
       <c r="B306" t="s">
-        <v>81</v>
+        <v>257</v>
       </c>
     </row>
     <row r="307" spans="1:2">
       <c r="A307" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="B307" t="s">
-        <v>152</v>
+        <v>373</v>
       </c>
     </row>
     <row r="308" spans="1:2">
       <c r="A308" t="s">
-        <v>21</v>
+        <v>374</v>
       </c>
       <c r="B308" t="s">
-        <v>375</v>
+        <v>203</v>
       </c>
     </row>
     <row r="309" spans="1:2">
       <c r="A309" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="B309" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
     </row>
     <row r="310" spans="1:2">
       <c r="A310" t="s">
-        <v>376</v>
+        <v>197</v>
       </c>
       <c r="B310" t="s">
-        <v>367</v>
+        <v>64</v>
       </c>
     </row>
     <row r="311" spans="1:2">
       <c r="A311" t="s">
-        <v>84</v>
+        <v>327</v>
       </c>
       <c r="B311" t="s">
-        <v>238</v>
+        <v>109</v>
       </c>
     </row>
     <row r="312" spans="1:2">
       <c r="A312" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B312" t="s">
-        <v>371</v>
+        <v>314</v>
       </c>
     </row>
     <row r="313" spans="1:2">
       <c r="A313" t="s">
-        <v>227</v>
+        <v>376</v>
       </c>
       <c r="B313" t="s">
-        <v>352</v>
+        <v>377</v>
       </c>
     </row>
     <row r="314" spans="1:2">
       <c r="A314" t="s">
-        <v>71</v>
+        <v>327</v>
       </c>
       <c r="B314" t="s">
-        <v>255</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315" spans="1:2">
       <c r="A315" t="s">
-        <v>378</v>
+        <v>69</v>
       </c>
       <c r="B315" t="s">
-        <v>379</v>
+        <v>265</v>
       </c>
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
-        <v>158</v>
+        <v>30</v>
       </c>
       <c r="B316" t="s">
-        <v>56</v>
+        <v>378</v>
       </c>
     </row>
     <row r="317" spans="1:2">
       <c r="A317" t="s">
-        <v>254</v>
+        <v>371</v>
       </c>
       <c r="B317" t="s">
-        <v>122</v>
+        <v>379</v>
       </c>
     </row>
     <row r="318" spans="1:2">
       <c r="A318" t="s">
+        <v>117</v>
+      </c>
+      <c r="B318" t="s">
         <v>380</v>
-      </c>
-      <c r="B318" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="319" spans="1:2">
       <c r="A319" t="s">
-        <v>311</v>
+        <v>381</v>
       </c>
       <c r="B319" t="s">
-        <v>67</v>
+        <v>315</v>
       </c>
     </row>
     <row r="320" spans="1:2">
       <c r="A320" t="s">
-        <v>136</v>
+        <v>382</v>
       </c>
       <c r="B320" t="s">
-        <v>381</v>
+        <v>224</v>
       </c>
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B321" t="s">
-        <v>210</v>
+        <v>384</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" t="s">
-        <v>321</v>
+        <v>284</v>
       </c>
       <c r="B322" t="s">
-        <v>126</v>
+        <v>385</v>
       </c>
     </row>
     <row r="323" spans="1:2">
       <c r="A323" t="s">
-        <v>86</v>
+        <v>386</v>
       </c>
       <c r="B323" t="s">
-        <v>258</v>
+        <v>387</v>
       </c>
     </row>
     <row r="324" spans="1:2">
       <c r="A324" t="s">
-        <v>218</v>
+        <v>152</v>
       </c>
       <c r="B324" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="325" spans="1:2">
       <c r="A325" t="s">
-        <v>383</v>
+        <v>228</v>
       </c>
       <c r="B325" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="326" spans="1:2">
       <c r="A326" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="B326" t="s">
-        <v>385</v>
+        <v>246</v>
       </c>
     </row>
     <row r="327" spans="1:2">
       <c r="A327" t="s">
-        <v>286</v>
+        <v>41</v>
       </c>
       <c r="B327" t="s">
-        <v>18</v>
+        <v>389</v>
       </c>
     </row>
     <row r="328" spans="1:2">
       <c r="A328" t="s">
-        <v>241</v>
+        <v>288</v>
       </c>
       <c r="B328" t="s">
-        <v>251</v>
+        <v>390</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B329" t="s">
-        <v>387</v>
+        <v>77</v>
       </c>
     </row>
     <row r="330" spans="1:2">
       <c r="A330" t="s">
-        <v>388</v>
+        <v>202</v>
       </c>
       <c r="B330" t="s">
-        <v>305</v>
+        <v>202</v>
       </c>
     </row>
     <row r="331" spans="1:2">
       <c r="A331" t="s">
-        <v>224</v>
+        <v>306</v>
       </c>
       <c r="B331" t="s">
-        <v>251</v>
+        <v>128</v>
       </c>
     </row>
     <row r="332" spans="1:2">
       <c r="A332" t="s">
-        <v>121</v>
+        <v>392</v>
       </c>
       <c r="B332" t="s">
-        <v>169</v>
+        <v>393</v>
       </c>
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
-        <v>386</v>
+        <v>317</v>
       </c>
       <c r="B333" t="s">
-        <v>23</v>
+        <v>235</v>
       </c>
     </row>
     <row r="334" spans="1:2">
       <c r="A334" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B334" t="s">
-        <v>330</v>
+        <v>103</v>
       </c>
     </row>
     <row r="335" spans="1:2">
       <c r="A335" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B335" t="s">
-        <v>51</v>
+        <v>395</v>
       </c>
     </row>
     <row r="336" spans="1:2">
       <c r="A336" t="s">
-        <v>390</v>
+        <v>237</v>
       </c>
       <c r="B336" t="s">
-        <v>355</v>
+        <v>396</v>
       </c>
     </row>
     <row r="337" spans="1:2">
       <c r="A337" t="s">
-        <v>103</v>
+        <v>293</v>
       </c>
       <c r="B337" t="s">
-        <v>93</v>
+        <v>394</v>
       </c>
     </row>
     <row r="338" spans="1:2">
       <c r="A338" t="s">
-        <v>304</v>
+        <v>397</v>
       </c>
       <c r="B338" t="s">
-        <v>215</v>
+        <v>130</v>
       </c>
     </row>
     <row r="339" spans="1:2">
       <c r="A339" t="s">
-        <v>267</v>
+        <v>108</v>
       </c>
       <c r="B339" t="s">
-        <v>29</v>
+        <v>398</v>
       </c>
     </row>
     <row r="340" spans="1:2">
       <c r="A340" t="s">
-        <v>386</v>
+        <v>278</v>
       </c>
       <c r="B340" t="s">
-        <v>214</v>
+        <v>159</v>
       </c>
     </row>
     <row r="341" spans="1:2">
       <c r="A341" t="s">
-        <v>391</v>
+        <v>151</v>
       </c>
       <c r="B341" t="s">
-        <v>247</v>
+        <v>198</v>
       </c>
     </row>
     <row r="342" spans="1:2">
       <c r="A342" t="s">
-        <v>268</v>
+        <v>102</v>
       </c>
       <c r="B342" t="s">
-        <v>392</v>
+        <v>200</v>
       </c>
     </row>
     <row r="343" spans="1:2">
       <c r="A343" t="s">
-        <v>362</v>
+        <v>16</v>
       </c>
       <c r="B343" t="s">
-        <v>248</v>
+        <v>282</v>
       </c>
     </row>
     <row r="344" spans="1:2">
       <c r="A344" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="B344" t="s">
-        <v>371</v>
+        <v>4</v>
       </c>
     </row>
     <row r="345" spans="1:2">
       <c r="A345" t="s">
-        <v>135</v>
+        <v>400</v>
       </c>
       <c r="B345" t="s">
-        <v>394</v>
+        <v>203</v>
       </c>
     </row>
     <row r="346" spans="1:2">
       <c r="A346" t="s">
-        <v>6</v>
+        <v>163</v>
       </c>
       <c r="B346" t="s">
-        <v>188</v>
+        <v>230</v>
       </c>
     </row>
     <row r="347" spans="1:2">
       <c r="A347" t="s">
-        <v>369</v>
+        <v>401</v>
       </c>
       <c r="B347" t="s">
-        <v>276</v>
+        <v>236</v>
       </c>
     </row>
     <row r="348" spans="1:2">
       <c r="A348" t="s">
-        <v>100</v>
+        <v>402</v>
       </c>
       <c r="B348" t="s">
-        <v>220</v>
+        <v>403</v>
       </c>
     </row>
     <row r="349" spans="1:2">
       <c r="A349" t="s">
-        <v>62</v>
+        <v>259</v>
       </c>
       <c r="B349" t="s">
-        <v>395</v>
+        <v>127</v>
       </c>
     </row>
     <row r="350" spans="1:2">
       <c r="A350" t="s">
-        <v>187</v>
+        <v>404</v>
       </c>
       <c r="B350" t="s">
-        <v>21</v>
+        <v>405</v>
       </c>
     </row>
     <row r="351" spans="1:2">
       <c r="A351" t="s">
-        <v>78</v>
+        <v>327</v>
       </c>
       <c r="B351" t="s">
-        <v>87</v>
+        <v>406</v>
       </c>
     </row>
     <row r="352" spans="1:2">
       <c r="A352" t="s">
-        <v>396</v>
+        <v>66</v>
       </c>
       <c r="B352" t="s">
-        <v>397</v>
+        <v>286</v>
       </c>
     </row>
     <row r="353" spans="1:2">
       <c r="A353" t="s">
-        <v>215</v>
+        <v>296</v>
       </c>
       <c r="B353" t="s">
-        <v>248</v>
+        <v>390</v>
       </c>
     </row>
     <row r="354" spans="1:2">
       <c r="A354" t="s">
-        <v>138</v>
+        <v>193</v>
       </c>
       <c r="B354" t="s">
-        <v>398</v>
+        <v>50</v>
       </c>
     </row>
     <row r="355" spans="1:2">
       <c r="A355" t="s">
-        <v>233</v>
+        <v>361</v>
       </c>
       <c r="B355" t="s">
-        <v>245</v>
+        <v>301</v>
       </c>
     </row>
     <row r="356" spans="1:2">
       <c r="A356" t="s">
-        <v>311</v>
+        <v>286</v>
       </c>
       <c r="B356" t="s">
-        <v>23</v>
+        <v>168</v>
       </c>
     </row>
     <row r="357" spans="1:2">
       <c r="A357" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="B357" t="s">
-        <v>168</v>
+        <v>257</v>
       </c>
     </row>
     <row r="358" spans="1:2">
       <c r="A358" t="s">
-        <v>15</v>
+        <v>408</v>
       </c>
       <c r="B358" t="s">
-        <v>400</v>
+        <v>354</v>
       </c>
     </row>
     <row r="359" spans="1:2">
       <c r="A359" t="s">
-        <v>300</v>
+        <v>409</v>
       </c>
       <c r="B359" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
     </row>
     <row r="360" spans="1:2">
       <c r="A360" t="s">
-        <v>243</v>
+        <v>301</v>
       </c>
       <c r="B360" t="s">
-        <v>84</v>
+        <v>273</v>
       </c>
     </row>
     <row r="361" spans="1:2">
       <c r="A361" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="B361" t="s">
-        <v>71</v>
+        <v>355</v>
       </c>
     </row>
     <row r="362" spans="1:2">
       <c r="A362" t="s">
-        <v>152</v>
+        <v>412</v>
       </c>
       <c r="B362" t="s">
-        <v>402</v>
+        <v>155</v>
       </c>
     </row>
     <row r="363" spans="1:2">
       <c r="A363" t="s">
-        <v>403</v>
+        <v>85</v>
       </c>
       <c r="B363" t="s">
-        <v>306</v>
+        <v>187</v>
       </c>
     </row>
     <row r="364" spans="1:2">
       <c r="A364" t="s">
-        <v>404</v>
+        <v>259</v>
       </c>
       <c r="B364" t="s">
-        <v>240</v>
+        <v>102</v>
       </c>
     </row>
     <row r="365" spans="1:2">
       <c r="A365" t="s">
-        <v>206</v>
+        <v>53</v>
       </c>
       <c r="B365" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
     </row>
     <row r="366" spans="1:2">
       <c r="A366" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="B366" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
     </row>
     <row r="367" spans="1:2">
       <c r="A367" t="s">
-        <v>209</v>
+        <v>34</v>
       </c>
       <c r="B367" t="s">
-        <v>380</v>
+        <v>413</v>
       </c>
     </row>
     <row r="368" spans="1:2">
       <c r="A368" t="s">
-        <v>214</v>
+        <v>414</v>
       </c>
       <c r="B368" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
     </row>
     <row r="369" spans="1:2">
       <c r="A369" t="s">
-        <v>406</v>
+        <v>13</v>
       </c>
       <c r="B369" t="s">
-        <v>189</v>
+        <v>139</v>
       </c>
     </row>
     <row r="370" spans="1:2">
       <c r="A370" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="B370" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
     </row>
     <row r="371" spans="1:2">
       <c r="A371" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B371" t="s">
-        <v>86</v>
+        <v>263</v>
       </c>
     </row>
     <row r="372" spans="1:2">
       <c r="A372" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B372" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="373" spans="1:2">
       <c r="A373" t="s">
-        <v>349</v>
+        <v>416</v>
       </c>
       <c r="B373" t="s">
-        <v>410</v>
+        <v>64</v>
       </c>
     </row>
     <row r="374" spans="1:2">
       <c r="A374" t="s">
-        <v>329</v>
+        <v>195</v>
       </c>
       <c r="B374" t="s">
-        <v>170</v>
+        <v>417</v>
       </c>
     </row>
     <row r="375" spans="1:2">
       <c r="A375" t="s">
-        <v>368</v>
+        <v>84</v>
       </c>
       <c r="B375" t="s">
-        <v>411</v>
+        <v>98</v>
       </c>
     </row>
     <row r="376" spans="1:2">
       <c r="A376" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="B376" t="s">
-        <v>338</v>
+        <v>418</v>
       </c>
     </row>
     <row r="377" spans="1:2">
       <c r="A377" t="s">
-        <v>87</v>
+        <v>419</v>
       </c>
       <c r="B377" t="s">
-        <v>150</v>
+        <v>216</v>
       </c>
     </row>
     <row r="378" spans="1:2">
       <c r="A378" t="s">
-        <v>412</v>
+        <v>172</v>
       </c>
       <c r="B378" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
     </row>
     <row r="379" spans="1:2">
       <c r="A379" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="B379" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
     </row>
     <row r="380" spans="1:2">
       <c r="A380" t="s">
-        <v>183</v>
+        <v>370</v>
       </c>
       <c r="B380" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="381" spans="1:2">
       <c r="A381" t="s">
-        <v>413</v>
+        <v>249</v>
       </c>
       <c r="B381" t="s">
-        <v>76</v>
+        <v>376</v>
       </c>
     </row>
     <row r="382" spans="1:2">
       <c r="A382" t="s">
-        <v>200</v>
+        <v>149</v>
       </c>
       <c r="B382" t="s">
-        <v>16</v>
+        <v>273</v>
       </c>
     </row>
     <row r="383" spans="1:2">
       <c r="A383" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B383" t="s">
-        <v>343</v>
+        <v>421</v>
       </c>
     </row>
     <row r="384" spans="1:2">
       <c r="A384" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="B384" t="s">
-        <v>379</v>
+        <v>123</v>
       </c>
     </row>
     <row r="385" spans="1:2">
       <c r="A385" t="s">
-        <v>8</v>
+        <v>423</v>
       </c>
       <c r="B385" t="s">
-        <v>415</v>
+        <v>191</v>
       </c>
     </row>
     <row r="386" spans="1:2">
       <c r="A386" t="s">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="B386" t="s">
-        <v>162</v>
+        <v>424</v>
       </c>
     </row>
     <row r="387" spans="1:2">
       <c r="A387" t="s">
-        <v>284</v>
+        <v>391</v>
       </c>
       <c r="B387" t="s">
-        <v>416</v>
+        <v>323</v>
       </c>
     </row>
     <row r="388" spans="1:2">
       <c r="A388" t="s">
-        <v>417</v>
+        <v>316</v>
       </c>
       <c r="B388" t="s">
-        <v>418</v>
+        <v>33</v>
       </c>
     </row>
     <row r="389" spans="1:2">
       <c r="A389" t="s">
-        <v>269</v>
+        <v>425</v>
       </c>
       <c r="B389" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
     </row>
     <row r="390" spans="1:2">
       <c r="A390" t="s">
-        <v>284</v>
+        <v>403</v>
       </c>
       <c r="B390" t="s">
-        <v>312</v>
+        <v>172</v>
       </c>
     </row>
     <row r="391" spans="1:2">
       <c r="A391" t="s">
-        <v>145</v>
+        <v>427</v>
       </c>
       <c r="B391" t="s">
-        <v>45</v>
+        <v>399</v>
       </c>
     </row>
     <row r="392" spans="1:2">
       <c r="A392" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="B392" t="s">
-        <v>421</v>
+        <v>185</v>
       </c>
     </row>
     <row r="393" spans="1:2">
       <c r="A393" t="s">
-        <v>167</v>
+        <v>221</v>
       </c>
       <c r="B393" t="s">
-        <v>287</v>
+        <v>142</v>
       </c>
     </row>
     <row r="394" spans="1:2">
       <c r="A394" t="s">
-        <v>136</v>
+        <v>232</v>
       </c>
       <c r="B394" t="s">
-        <v>214</v>
+        <v>69</v>
       </c>
     </row>
     <row r="395" spans="1:2">
       <c r="A395" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="B395" t="s">
-        <v>417</v>
+        <v>184</v>
       </c>
     </row>
     <row r="396" spans="1:2">
       <c r="A396" t="s">
-        <v>47</v>
+        <v>333</v>
       </c>
       <c r="B396" t="s">
-        <v>235</v>
+        <v>283</v>
       </c>
     </row>
     <row r="397" spans="1:2">
       <c r="A397" t="s">
-        <v>388</v>
+        <v>321</v>
       </c>
       <c r="B397" t="s">
-        <v>110</v>
+        <v>27</v>
       </c>
     </row>
     <row r="398" spans="1:2">
       <c r="A398" t="s">
-        <v>271</v>
+        <v>226</v>
       </c>
       <c r="B398" t="s">
-        <v>89</v>
+        <v>430</v>
       </c>
     </row>
     <row r="399" spans="1:2">
       <c r="A399" t="s">
-        <v>125</v>
+        <v>431</v>
       </c>
       <c r="B399" t="s">
-        <v>297</v>
+        <v>325</v>
       </c>
     </row>
     <row r="400" spans="1:2">
       <c r="A400" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B400" t="s">
-        <v>318</v>
+        <v>71</v>
       </c>
     </row>
     <row r="401" spans="1:2">
       <c r="A401" t="s">
-        <v>212</v>
+        <v>50</v>
       </c>
       <c r="B401" t="s">
-        <v>142</v>
+        <v>28</v>
       </c>
     </row>
     <row r="402" spans="1:2">
       <c r="A402" t="s">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="B402" t="s">
-        <v>424</v>
+        <v>392</v>
       </c>
     </row>
     <row r="403" spans="1:2">
       <c r="A403" t="s">
-        <v>425</v>
+        <v>316</v>
       </c>
       <c r="B403" t="s">
-        <v>324</v>
+        <v>432</v>
       </c>
     </row>
     <row r="404" spans="1:2">
       <c r="A404" t="s">
-        <v>88</v>
+        <v>433</v>
       </c>
       <c r="B404" t="s">
-        <v>394</v>
+        <v>118</v>
       </c>
     </row>
     <row r="405" spans="1:2">
       <c r="A405" t="s">
-        <v>334</v>
+        <v>273</v>
       </c>
       <c r="B405" t="s">
-        <v>293</v>
+        <v>149</v>
       </c>
     </row>
     <row r="406" spans="1:2">
       <c r="A406" t="s">
-        <v>200</v>
+        <v>76</v>
       </c>
       <c r="B406" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="407" spans="1:2">
       <c r="A407" t="s">
-        <v>255</v>
+        <v>320</v>
       </c>
       <c r="B407" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="408" spans="1:2">
       <c r="A408" t="s">
-        <v>136</v>
+        <v>191</v>
       </c>
       <c r="B408" t="s">
-        <v>271</v>
+        <v>190</v>
       </c>
     </row>
     <row r="409" spans="1:2">
       <c r="A409" t="s">
-        <v>427</v>
+        <v>90</v>
       </c>
       <c r="B409" t="s">
-        <v>118</v>
+        <v>376</v>
       </c>
     </row>
     <row r="410" spans="1:2">
       <c r="A410" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="B410" t="s">
-        <v>198</v>
+        <v>77</v>
       </c>
     </row>
     <row r="411" spans="1:2">
       <c r="A411" t="s">
-        <v>169</v>
+        <v>407</v>
       </c>
       <c r="B411" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
     </row>
     <row r="412" spans="1:2">
       <c r="A412" t="s">
-        <v>416</v>
+        <v>159</v>
       </c>
       <c r="B412" t="s">
-        <v>384</v>
+        <v>207</v>
       </c>
     </row>
     <row r="413" spans="1:2">
       <c r="A413" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="B413" t="s">
-        <v>430</v>
+        <v>378</v>
       </c>
     </row>
     <row r="414" spans="1:2">
       <c r="A414" t="s">
-        <v>361</v>
+        <v>161</v>
       </c>
       <c r="B414" t="s">
-        <v>141</v>
+        <v>396</v>
       </c>
     </row>
     <row r="415" spans="1:2">
       <c r="A415" t="s">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="B415" t="s">
-        <v>235</v>
+        <v>313</v>
       </c>
     </row>
     <row r="416" spans="1:2">
       <c r="A416" t="s">
-        <v>379</v>
+        <v>437</v>
       </c>
       <c r="B416" t="s">
-        <v>112</v>
+        <v>438</v>
       </c>
     </row>
     <row r="417" spans="1:2">
       <c r="A417" t="s">
-        <v>220</v>
+        <v>439</v>
       </c>
       <c r="B417" t="s">
-        <v>431</v>
+        <v>283</v>
       </c>
     </row>
     <row r="418" spans="1:2">
       <c r="A418" t="s">
-        <v>296</v>
+        <v>371</v>
       </c>
       <c r="B418" t="s">
-        <v>119</v>
+        <v>328</v>
       </c>
     </row>
     <row r="419" spans="1:2">
       <c r="A419" t="s">
-        <v>185</v>
+        <v>418</v>
       </c>
       <c r="B419" t="s">
-        <v>306</v>
+        <v>440</v>
       </c>
     </row>
     <row r="420" spans="1:2">
       <c r="A420" t="s">
-        <v>376</v>
+        <v>441</v>
       </c>
       <c r="B420" t="s">
-        <v>263</v>
+        <v>192</v>
       </c>
     </row>
     <row r="421" spans="1:2">
       <c r="A421" t="s">
-        <v>421</v>
+        <v>243</v>
       </c>
       <c r="B421" t="s">
-        <v>135</v>
+        <v>442</v>
       </c>
     </row>
     <row r="422" spans="1:2">
       <c r="A422" t="s">
-        <v>370</v>
+        <v>443</v>
       </c>
       <c r="B422" t="s">
-        <v>432</v>
+        <v>210</v>
       </c>
     </row>
     <row r="423" spans="1:2">
       <c r="A423" t="s">
-        <v>34</v>
+        <v>333</v>
       </c>
       <c r="B423" t="s">
-        <v>433</v>
+        <v>254</v>
       </c>
     </row>
     <row r="424" spans="1:2">
       <c r="A424" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="B424" t="s">
-        <v>334</v>
+        <v>211</v>
       </c>
     </row>
     <row r="425" spans="1:2">
       <c r="A425" t="s">
-        <v>284</v>
+        <v>444</v>
       </c>
       <c r="B425" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
     </row>
     <row r="426" spans="1:2">
       <c r="A426" t="s">
-        <v>7</v>
+        <v>333</v>
       </c>
       <c r="B426" t="s">
-        <v>138</v>
+        <v>174</v>
       </c>
     </row>
     <row r="427" spans="1:2">
       <c r="A427" t="s">
-        <v>205</v>
+        <v>428</v>
       </c>
       <c r="B427" t="s">
-        <v>13</v>
+        <v>323</v>
       </c>
     </row>
     <row r="428" spans="1:2">
       <c r="A428" t="s">
-        <v>357</v>
+        <v>57</v>
       </c>
       <c r="B428" t="s">
-        <v>77</v>
+        <v>291</v>
       </c>
     </row>
     <row r="429" spans="1:2">
       <c r="A429" t="s">
-        <v>229</v>
+        <v>446</v>
       </c>
       <c r="B429" t="s">
-        <v>278</v>
+        <v>76</v>
       </c>
     </row>
     <row r="430" spans="1:2">
       <c r="A430" t="s">
-        <v>117</v>
+        <v>238</v>
       </c>
       <c r="B430" t="s">
-        <v>243</v>
+        <v>447</v>
       </c>
     </row>
     <row r="431" spans="1:2">
       <c r="A431" t="s">
-        <v>401</v>
+        <v>329</v>
       </c>
       <c r="B431" t="s">
-        <v>225</v>
+        <v>445</v>
       </c>
     </row>
     <row r="432" spans="1:2">
       <c r="A432" t="s">
-        <v>339</v>
+        <v>245</v>
       </c>
       <c r="B432" t="s">
-        <v>435</v>
+        <v>448</v>
       </c>
     </row>
     <row r="433" spans="1:2">
       <c r="A433" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="B433" t="s">
-        <v>186</v>
+        <v>369</v>
       </c>
     </row>
     <row r="434" spans="1:2">
       <c r="A434" t="s">
-        <v>155</v>
+        <v>343</v>
       </c>
       <c r="B434" t="s">
-        <v>437</v>
+        <v>450</v>
       </c>
     </row>
     <row r="435" spans="1:2">
       <c r="A435" t="s">
-        <v>225</v>
+        <v>334</v>
       </c>
       <c r="B435" t="s">
-        <v>144</v>
+        <v>308</v>
       </c>
     </row>
     <row r="436" spans="1:2">
       <c r="A436" t="s">
-        <v>80</v>
+        <v>451</v>
       </c>
       <c r="B436" t="s">
-        <v>238</v>
+        <v>452</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" t="s">
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="B437" t="s">
-        <v>436</v>
+        <v>414</v>
       </c>
     </row>
     <row r="438" spans="1:2">
       <c r="A438" t="s">
-        <v>172</v>
+        <v>34</v>
       </c>
       <c r="B438" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
     </row>
     <row r="439" spans="1:2">
       <c r="A439" t="s">
-        <v>438</v>
+        <v>165</v>
       </c>
       <c r="B439" t="s">
-        <v>198</v>
+        <v>255</v>
       </c>
     </row>
     <row r="440" spans="1:2">
       <c r="A440" t="s">
-        <v>351</v>
+        <v>409</v>
       </c>
       <c r="B440" t="s">
-        <v>299</v>
+        <v>453</v>
       </c>
     </row>
     <row r="441" spans="1:2">
       <c r="A441" t="s">
-        <v>439</v>
+        <v>124</v>
       </c>
       <c r="B441" t="s">
-        <v>102</v>
+        <v>160</v>
       </c>
     </row>
     <row r="442" spans="1:2">
       <c r="A442" t="s">
-        <v>326</v>
+        <v>94</v>
       </c>
       <c r="B442" t="s">
-        <v>223</v>
+        <v>73</v>
       </c>
     </row>
     <row r="443" spans="1:2">
       <c r="A443" t="s">
-        <v>200</v>
+        <v>343</v>
       </c>
       <c r="B443" t="s">
-        <v>424</v>
+        <v>153</v>
       </c>
     </row>
     <row r="444" spans="1:2">
       <c r="A444" t="s">
-        <v>337</v>
+        <v>245</v>
       </c>
       <c r="B444" t="s">
-        <v>85</v>
+        <v>205</v>
       </c>
     </row>
     <row r="445" spans="1:2">
       <c r="A445" t="s">
-        <v>148</v>
+        <v>432</v>
       </c>
       <c r="B445" t="s">
-        <v>317</v>
+        <v>454</v>
       </c>
     </row>
     <row r="446" spans="1:2">
       <c r="A446" t="s">
-        <v>37</v>
+        <v>196</v>
       </c>
       <c r="B446" t="s">
-        <v>187</v>
+        <v>299</v>
       </c>
     </row>
     <row r="447" spans="1:2">
       <c r="A447" t="s">
-        <v>440</v>
+        <v>5</v>
       </c>
       <c r="B447" t="s">
-        <v>203</v>
+        <v>140</v>
       </c>
     </row>
     <row r="448" spans="1:2">
       <c r="A448" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B448" t="s">
-        <v>427</v>
+        <v>360</v>
       </c>
     </row>
     <row r="449" spans="1:2">
       <c r="A449" t="s">
-        <v>441</v>
+        <v>56</v>
       </c>
       <c r="B449" t="s">
-        <v>338</v>
+        <v>455</v>
       </c>
     </row>
     <row r="450" spans="1:2">
       <c r="A450" t="s">
-        <v>442</v>
+        <v>245</v>
       </c>
       <c r="B450" t="s">
-        <v>298</v>
+        <v>268</v>
       </c>
     </row>
     <row r="451" spans="1:2">
       <c r="A451" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B451" t="s">
-        <v>383</v>
+        <v>205</v>
       </c>
     </row>
     <row r="452" spans="1:2">
       <c r="A452" t="s">
-        <v>443</v>
+        <v>90</v>
       </c>
       <c r="B452" t="s">
-        <v>272</v>
+        <v>27</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -5400,679 +5451,727 @@
         <v>190</v>
       </c>
       <c r="B453" t="s">
-        <v>305</v>
+        <v>24</v>
       </c>
     </row>
     <row r="454" spans="1:2">
       <c r="A454" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="B454" t="s">
-        <v>264</v>
+        <v>457</v>
       </c>
     </row>
     <row r="455" spans="1:2">
       <c r="A455" t="s">
-        <v>80</v>
+        <v>458</v>
       </c>
       <c r="B455" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
     </row>
     <row r="456" spans="1:2">
       <c r="A456" t="s">
-        <v>144</v>
+        <v>460</v>
       </c>
       <c r="B456" t="s">
-        <v>446</v>
+        <v>85</v>
       </c>
     </row>
     <row r="457" spans="1:2">
       <c r="A457" t="s">
-        <v>126</v>
+        <v>461</v>
       </c>
       <c r="B457" t="s">
-        <v>447</v>
+        <v>46</v>
       </c>
     </row>
     <row r="458" spans="1:2">
       <c r="A458" t="s">
-        <v>324</v>
+        <v>83</v>
       </c>
       <c r="B458" t="s">
-        <v>253</v>
+        <v>462</v>
       </c>
     </row>
     <row r="459" spans="1:2">
       <c r="A459" t="s">
-        <v>20</v>
+        <v>463</v>
       </c>
       <c r="B459" t="s">
-        <v>263</v>
+        <v>58</v>
       </c>
     </row>
     <row r="460" spans="1:2">
       <c r="A460" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="B460" t="s">
-        <v>374</v>
+        <v>464</v>
       </c>
     </row>
     <row r="461" spans="1:2">
       <c r="A461" t="s">
-        <v>400</v>
+        <v>159</v>
       </c>
       <c r="B461" t="s">
-        <v>47</v>
+        <v>241</v>
       </c>
     </row>
     <row r="462" spans="1:2">
       <c r="A462" t="s">
-        <v>199</v>
+        <v>465</v>
       </c>
       <c r="B462" t="s">
-        <v>259</v>
+        <v>462</v>
       </c>
     </row>
     <row r="463" spans="1:2">
       <c r="A463" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="B463" t="s">
-        <v>167</v>
+        <v>331</v>
       </c>
     </row>
     <row r="464" spans="1:2">
       <c r="A464" t="s">
-        <v>281</v>
+        <v>185</v>
       </c>
       <c r="B464" t="s">
-        <v>449</v>
+        <v>257</v>
       </c>
     </row>
     <row r="465" spans="1:2">
       <c r="A465" t="s">
-        <v>126</v>
+        <v>241</v>
       </c>
       <c r="B465" t="s">
-        <v>430</v>
+        <v>337</v>
       </c>
     </row>
     <row r="466" spans="1:2">
       <c r="A466" t="s">
-        <v>409</v>
+        <v>67</v>
       </c>
       <c r="B466" t="s">
-        <v>310</v>
+        <v>218</v>
       </c>
     </row>
     <row r="467" spans="1:2">
       <c r="A467" t="s">
-        <v>411</v>
+        <v>143</v>
       </c>
       <c r="B467" t="s">
-        <v>322</v>
+        <v>363</v>
       </c>
     </row>
     <row r="468" spans="1:2">
       <c r="A468" t="s">
-        <v>299</v>
+        <v>89</v>
       </c>
       <c r="B468" t="s">
-        <v>83</v>
+        <v>467</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>30</v>
+        <v>111</v>
       </c>
       <c r="B469" t="s">
-        <v>450</v>
+        <v>203</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
-        <v>437</v>
+        <v>468</v>
       </c>
       <c r="B470" t="s">
-        <v>260</v>
+        <v>313</v>
       </c>
     </row>
     <row r="471" spans="1:2">
       <c r="A471" t="s">
-        <v>97</v>
+        <v>147</v>
       </c>
       <c r="B471" t="s">
-        <v>275</v>
+        <v>362</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" t="s">
-        <v>429</v>
+        <v>116</v>
       </c>
       <c r="B472" t="s">
-        <v>320</v>
+        <v>16</v>
       </c>
     </row>
     <row r="473" spans="1:2">
       <c r="A473" t="s">
-        <v>165</v>
+        <v>100</v>
       </c>
       <c r="B473" t="s">
-        <v>252</v>
+        <v>149</v>
       </c>
     </row>
     <row r="474" spans="1:2">
       <c r="A474" t="s">
-        <v>451</v>
+        <v>151</v>
       </c>
       <c r="B474" t="s">
-        <v>452</v>
+        <v>203</v>
       </c>
     </row>
     <row r="475" spans="1:2">
       <c r="A475" t="s">
-        <v>175</v>
+        <v>469</v>
       </c>
       <c r="B475" t="s">
-        <v>309</v>
+        <v>101</v>
       </c>
     </row>
     <row r="476" spans="1:2">
       <c r="A476" t="s">
-        <v>6</v>
+        <v>152</v>
       </c>
       <c r="B476" t="s">
-        <v>453</v>
+        <v>87</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
-        <v>203</v>
+        <v>380</v>
       </c>
       <c r="B477" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="478" spans="1:2">
       <c r="A478" t="s">
-        <v>274</v>
+        <v>100</v>
       </c>
       <c r="B478" t="s">
-        <v>454</v>
+        <v>470</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" t="s">
-        <v>203</v>
+        <v>386</v>
       </c>
       <c r="B479" t="s">
-        <v>405</v>
+        <v>471</v>
       </c>
     </row>
     <row r="480" spans="1:2">
       <c r="A480" t="s">
-        <v>332</v>
+        <v>355</v>
       </c>
       <c r="B480" t="s">
-        <v>455</v>
+        <v>374</v>
       </c>
     </row>
     <row r="481" spans="1:2">
       <c r="A481" t="s">
-        <v>456</v>
+        <v>182</v>
       </c>
       <c r="B481" t="s">
-        <v>419</v>
+        <v>89</v>
       </c>
     </row>
     <row r="482" spans="1:2">
       <c r="A482" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="B482" t="s">
-        <v>183</v>
+        <v>295</v>
       </c>
     </row>
     <row r="483" spans="1:2">
       <c r="A483" t="s">
-        <v>403</v>
+        <v>21</v>
       </c>
       <c r="B483" t="s">
-        <v>57</v>
+        <v>243</v>
       </c>
     </row>
     <row r="484" spans="1:2">
       <c r="A484" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="B484" t="s">
-        <v>242</v>
+        <v>73</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>457</v>
+        <v>113</v>
       </c>
       <c r="B485" t="s">
-        <v>122</v>
+        <v>452</v>
       </c>
     </row>
     <row r="486" spans="1:2">
       <c r="A486" t="s">
-        <v>458</v>
+        <v>282</v>
       </c>
       <c r="B486" t="s">
-        <v>459</v>
+        <v>83</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>101</v>
+        <v>339</v>
       </c>
       <c r="B487" t="s">
-        <v>39</v>
+        <v>340</v>
       </c>
     </row>
     <row r="488" spans="1:2">
       <c r="A488" t="s">
-        <v>317</v>
+        <v>472</v>
       </c>
       <c r="B488" t="s">
-        <v>460</v>
+        <v>413</v>
       </c>
     </row>
     <row r="489" spans="1:2">
       <c r="A489" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="B489" t="s">
-        <v>461</v>
+        <v>384</v>
       </c>
     </row>
     <row r="490" spans="1:2">
       <c r="A490" t="s">
-        <v>40</v>
+        <v>473</v>
       </c>
       <c r="B490" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
     </row>
     <row r="491" spans="1:2">
       <c r="A491" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="B491" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" t="s">
-        <v>311</v>
+        <v>210</v>
       </c>
       <c r="B492" t="s">
-        <v>124</v>
+        <v>27</v>
       </c>
     </row>
     <row r="493" spans="1:2">
       <c r="A493" t="s">
-        <v>364</v>
+        <v>474</v>
       </c>
       <c r="B493" t="s">
-        <v>203</v>
+        <v>8</v>
       </c>
     </row>
     <row r="494" spans="1:2">
       <c r="A494" t="s">
-        <v>342</v>
+        <v>475</v>
       </c>
       <c r="B494" t="s">
-        <v>251</v>
+        <v>25</v>
       </c>
     </row>
     <row r="495" spans="1:2">
       <c r="A495" t="s">
-        <v>453</v>
+        <v>255</v>
       </c>
       <c r="B495" t="s">
-        <v>293</v>
+        <v>108</v>
       </c>
     </row>
     <row r="496" spans="1:2">
       <c r="A496" t="s">
-        <v>245</v>
+        <v>476</v>
       </c>
       <c r="B496" t="s">
-        <v>462</v>
+        <v>301</v>
       </c>
     </row>
     <row r="497" spans="1:2">
       <c r="A497" t="s">
-        <v>326</v>
+        <v>240</v>
       </c>
       <c r="B497" t="s">
-        <v>211</v>
+        <v>449</v>
       </c>
     </row>
     <row r="498" spans="1:2">
       <c r="A498" t="s">
-        <v>49</v>
+        <v>270</v>
       </c>
       <c r="B498" t="s">
-        <v>298</v>
+        <v>322</v>
       </c>
     </row>
     <row r="499" spans="1:2">
       <c r="A499" t="s">
-        <v>461</v>
+        <v>477</v>
       </c>
       <c r="B499" t="s">
-        <v>59</v>
+        <v>343</v>
       </c>
     </row>
     <row r="500" spans="1:2">
       <c r="A500" t="s">
-        <v>414</v>
+        <v>478</v>
       </c>
       <c r="B500" t="s">
-        <v>3</v>
+        <v>479</v>
       </c>
     </row>
     <row r="501" spans="1:2">
       <c r="A501" t="s">
-        <v>455</v>
+        <v>257</v>
       </c>
       <c r="B501" t="s">
-        <v>268</v>
+        <v>480</v>
       </c>
     </row>
     <row r="502" spans="1:2">
       <c r="A502" t="s">
-        <v>99</v>
+        <v>346</v>
       </c>
       <c r="B502" t="s">
-        <v>162</v>
+        <v>481</v>
       </c>
     </row>
     <row r="503" spans="1:2">
       <c r="A503" t="s">
-        <v>463</v>
+        <v>73</v>
       </c>
       <c r="B503" t="s">
-        <v>201</v>
+        <v>400</v>
       </c>
     </row>
     <row r="504" spans="1:2">
       <c r="A504" t="s">
-        <v>211</v>
+        <v>470</v>
       </c>
       <c r="B504" t="s">
-        <v>84</v>
+        <v>482</v>
       </c>
     </row>
     <row r="505" spans="1:2">
       <c r="A505" t="s">
-        <v>186</v>
+        <v>120</v>
       </c>
       <c r="B505" t="s">
-        <v>228</v>
+        <v>483</v>
       </c>
     </row>
     <row r="506" spans="1:2">
       <c r="A506" t="s">
-        <v>372</v>
+        <v>198</v>
       </c>
       <c r="B506" t="s">
-        <v>364</v>
+        <v>215</v>
       </c>
     </row>
     <row r="507" spans="1:2">
       <c r="A507" t="s">
-        <v>82</v>
+        <v>484</v>
       </c>
       <c r="B507" t="s">
-        <v>119</v>
+        <v>213</v>
       </c>
     </row>
     <row r="508" spans="1:2">
       <c r="A508" t="s">
-        <v>464</v>
+        <v>343</v>
       </c>
       <c r="B508" t="s">
-        <v>65</v>
+        <v>443</v>
       </c>
     </row>
     <row r="509" spans="1:2">
       <c r="A509" t="s">
-        <v>249</v>
+        <v>470</v>
       </c>
       <c r="B509" t="s">
-        <v>251</v>
+        <v>302</v>
       </c>
     </row>
     <row r="510" spans="1:2">
       <c r="A510" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B510" t="s">
-        <v>17</v>
+        <v>485</v>
       </c>
     </row>
     <row r="511" spans="1:2">
       <c r="A511" t="s">
-        <v>386</v>
+        <v>486</v>
       </c>
       <c r="B511" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
     </row>
     <row r="512" spans="1:2">
       <c r="A512" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="B512" t="s">
-        <v>7</v>
+        <v>487</v>
       </c>
     </row>
     <row r="513" spans="1:2">
       <c r="A513" t="s">
-        <v>176</v>
+        <v>30</v>
       </c>
       <c r="B513" t="s">
-        <v>84</v>
+        <v>394</v>
       </c>
     </row>
     <row r="514" spans="1:2">
       <c r="A514" t="s">
-        <v>236</v>
+        <v>481</v>
       </c>
       <c r="B514" t="s">
-        <v>465</v>
+        <v>264</v>
       </c>
     </row>
     <row r="515" spans="1:2">
       <c r="A515" t="s">
-        <v>359</v>
+        <v>41</v>
       </c>
       <c r="B515" t="s">
-        <v>466</v>
+        <v>399</v>
       </c>
     </row>
     <row r="516" spans="1:2">
       <c r="A516" t="s">
-        <v>467</v>
+        <v>159</v>
       </c>
       <c r="B516" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
     </row>
     <row r="517" spans="1:2">
       <c r="A517" t="s">
-        <v>331</v>
+        <v>119</v>
       </c>
       <c r="B517" t="s">
-        <v>407</v>
+        <v>485</v>
       </c>
     </row>
     <row r="518" spans="1:2">
       <c r="A518" t="s">
-        <v>468</v>
+        <v>273</v>
       </c>
       <c r="B518" t="s">
-        <v>388</v>
+        <v>71</v>
       </c>
     </row>
     <row r="519" spans="1:2">
       <c r="A519" t="s">
-        <v>268</v>
+        <v>371</v>
       </c>
       <c r="B519" t="s">
-        <v>50</v>
+        <v>488</v>
       </c>
     </row>
     <row r="520" spans="1:2">
       <c r="A520" t="s">
-        <v>126</v>
+        <v>225</v>
       </c>
       <c r="B520" t="s">
-        <v>375</v>
+        <v>198</v>
       </c>
     </row>
     <row r="521" spans="1:2">
       <c r="A521" t="s">
-        <v>383</v>
+        <v>76</v>
       </c>
       <c r="B521" t="s">
-        <v>469</v>
+        <v>323</v>
       </c>
     </row>
     <row r="522" spans="1:2">
       <c r="A522" t="s">
-        <v>470</v>
+        <v>290</v>
       </c>
       <c r="B522" t="s">
-        <v>354</v>
+        <v>298</v>
       </c>
     </row>
     <row r="523" spans="1:2">
       <c r="A523" t="s">
-        <v>361</v>
+        <v>489</v>
       </c>
       <c r="B523" t="s">
-        <v>319</v>
+        <v>198</v>
       </c>
     </row>
     <row r="524" spans="1:2">
       <c r="A524" t="s">
-        <v>273</v>
+        <v>171</v>
       </c>
       <c r="B524" t="s">
-        <v>266</v>
+        <v>470</v>
       </c>
     </row>
     <row r="525" spans="1:2">
       <c r="A525" t="s">
-        <v>448</v>
+        <v>33</v>
       </c>
       <c r="B525" t="s">
-        <v>471</v>
+        <v>37</v>
       </c>
     </row>
     <row r="526" spans="1:2">
       <c r="A526" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="B526" t="s">
-        <v>421</v>
+        <v>471</v>
       </c>
     </row>
     <row r="527" spans="1:2">
       <c r="A527" t="s">
-        <v>364</v>
+        <v>331</v>
       </c>
       <c r="B527" t="s">
-        <v>472</v>
+        <v>356</v>
       </c>
     </row>
     <row r="528" spans="1:2">
       <c r="A528" t="s">
-        <v>279</v>
+        <v>490</v>
       </c>
       <c r="B528" t="s">
-        <v>421</v>
+        <v>375</v>
       </c>
     </row>
     <row r="529" spans="1:2">
       <c r="A529" t="s">
-        <v>473</v>
+        <v>111</v>
       </c>
       <c r="B529" t="s">
-        <v>474</v>
+        <v>243</v>
       </c>
     </row>
     <row r="530" spans="1:2">
       <c r="A530" t="s">
-        <v>410</v>
+        <v>380</v>
       </c>
       <c r="B530" t="s">
-        <v>475</v>
+        <v>435</v>
       </c>
     </row>
     <row r="531" spans="1:2">
       <c r="A531" t="s">
-        <v>33</v>
+        <v>249</v>
       </c>
       <c r="B531" t="s">
-        <v>204</v>
+        <v>290</v>
       </c>
     </row>
     <row r="532" spans="1:2">
       <c r="A532" t="s">
-        <v>476</v>
+        <v>244</v>
       </c>
       <c r="B532" t="s">
-        <v>216</v>
+        <v>360</v>
       </c>
     </row>
     <row r="533" spans="1:2">
       <c r="A533" t="s">
-        <v>196</v>
+        <v>453</v>
       </c>
       <c r="B533" t="s">
-        <v>434</v>
+        <v>331</v>
       </c>
     </row>
     <row r="534" spans="1:2">
       <c r="A534" t="s">
-        <v>33</v>
+        <v>491</v>
       </c>
       <c r="B534" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="535" spans="1:2">
       <c r="A535" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="B535" t="s">
-        <v>392</v>
+        <v>155</v>
       </c>
     </row>
     <row r="536" spans="1:2">
       <c r="A536" t="s">
-        <v>238</v>
+        <v>492</v>
       </c>
       <c r="B536" t="s">
-        <v>468</v>
+        <v>493</v>
       </c>
     </row>
     <row r="537" spans="1:2">
       <c r="A537" t="s">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="B537" t="s">
-        <v>287</v>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538" t="s">
+        <v>145</v>
+      </c>
+      <c r="B538" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539" t="s">
+        <v>155</v>
+      </c>
+      <c r="B539" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540" t="s">
+        <v>452</v>
+      </c>
+      <c r="B540" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541" t="s">
+        <v>251</v>
+      </c>
+      <c r="B541" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542" t="s">
+        <v>301</v>
+      </c>
+      <c r="B542" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543" t="s">
+        <v>422</v>
+      </c>
+      <c r="B543" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
